--- a/research_materials/03_results/robustness_gap.xlsx
+++ b/research_materials/03_results/robustness_gap.xlsx
@@ -459,7 +459,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Built: 2026-10-06 21:47 by src/build_research_materials.py</t>
+          <t>Built: 2026-10-06 23:35 by src/build_research_materials.py</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L67"/>
+  <dimension ref="A1:L139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
@@ -720,7 +720,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__concise40</t>
+          <t>gemma-4-e4b-it__base__rerender</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -730,12 +730,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>concise40</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>rerender</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -743,32 +743,20 @@
           <t>judge_lenient</t>
         </is>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>-0.039</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>-0.075</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>-0.004</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>0.035</v>
-      </c>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="3" t="n"/>
+      <c r="J5" s="3" t="n"/>
+      <c r="K5" s="3" t="n"/>
       <c r="L5" s="2" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__concise40</t>
+          <t>gemma-4-e4b-it__base__rerender</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -778,12 +766,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>concise40</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>rerender</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -791,32 +779,20 @@
           <t>keyfact_recall</t>
         </is>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>0.309</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>0.303</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>-0.027</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>0.6870000000000001</v>
-      </c>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="n"/>
+      <c r="K6" s="3" t="n"/>
       <c r="L6" s="2" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__concise40</t>
+          <t>gemma-4-e4b-it__base__rerender</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -826,12 +802,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>concise40</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>rerender</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -840,22 +816,22 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.639</v>
+        <v>1</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>279</v>
@@ -864,7 +840,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__cpt_ep1__bf16serve</t>
+          <t>gemma-4-e4b-it__concise40</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -874,12 +850,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>cpt_ep1</t>
+          <t>concise40</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -888,22 +864,22 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.52</v>
+        <v>0.556</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.554</v>
+        <v>0.595</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.034</v>
+        <v>-0.039</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.068</v>
+        <v>-0.075</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0</v>
+        <v>-0.004</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.058</v>
+        <v>0.035</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>279</v>
@@ -912,7 +888,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__cpt_ep1__bf16serve</t>
+          <t>gemma-4-e4b-it__concise40</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -922,12 +898,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>cpt_ep1</t>
+          <t>concise40</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -936,13 +912,13 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.322</v>
+        <v>0.309</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.317</v>
+        <v>0.303</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.006</v>
+        <v>0.007</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>-0.027</v>
@@ -951,7 +927,7 @@
         <v>0.04</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0.75</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>279</v>
@@ -960,7 +936,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__cpt_ep1__bf16serve</t>
+          <t>gemma-4-e4b-it__concise40</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -970,12 +946,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>cpt_ep1</t>
+          <t>concise40</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -984,22 +960,22 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.014</v>
+        <v>0.004</v>
       </c>
       <c r="G10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3" t="n">
         <v>0.004</v>
       </c>
-      <c r="H10" s="3" t="n">
+      <c r="I10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="n">
         <v>0.011</v>
       </c>
-      <c r="I10" s="3" t="n">
-        <v>-0.004</v>
-      </c>
-      <c r="J10" s="3" t="n">
-        <v>0.029</v>
-      </c>
       <c r="K10" s="3" t="n">
-        <v>0.257</v>
+        <v>0.639</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>279</v>
@@ -1008,7 +984,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__ep1__bf16serve</t>
+          <t>gemma-4-e4b-it__concise40__rerender</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1018,12 +994,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>ep1</t>
+          <t>concise40</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>rerender</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1031,32 +1007,20 @@
           <t>judge_lenient</t>
         </is>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>0.541</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>-0.054</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>-0.095</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>-0.016</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>0.006</v>
-      </c>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="3" t="n"/>
+      <c r="K11" s="3" t="n"/>
       <c r="L11" s="2" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__ep1__bf16serve</t>
+          <t>gemma-4-e4b-it__concise40__rerender</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1066,12 +1030,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>ep1</t>
+          <t>concise40</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>rerender</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1079,32 +1043,20 @@
           <t>keyfact_recall</t>
         </is>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>0.362</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>0.359</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>-0.036</v>
-      </c>
-      <c r="J12" s="3" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="K12" s="3" t="n">
-        <v>0.873</v>
-      </c>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+      <c r="I12" s="3" t="n"/>
+      <c r="J12" s="3" t="n"/>
+      <c r="K12" s="3" t="n"/>
       <c r="L12" s="2" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__ep1__bf16serve</t>
+          <t>gemma-4-e4b-it__concise40__rerender</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1114,12 +1066,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>ep1</t>
+          <t>concise40</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>rerender</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1128,22 +1080,22 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0.011</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.032</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0.415</v>
+        <v>1</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>279</v>
@@ -1152,7 +1104,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__ep2__bf16serve</t>
+          <t>gemma-4-e4b-it__cpt_ep1</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1162,12 +1114,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>ep2</t>
+          <t>cpt_ep1</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1175,32 +1127,20 @@
           <t>judge_lenient</t>
         </is>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>0.586</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>0.599</v>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>-0.013</v>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>-0.054</v>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>0.597</v>
-      </c>
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+      <c r="I14" s="3" t="n"/>
+      <c r="J14" s="3" t="n"/>
+      <c r="K14" s="3" t="n"/>
       <c r="L14" s="2" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__ep2__bf16serve</t>
+          <t>gemma-4-e4b-it__cpt_ep1</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1210,12 +1150,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>ep2</t>
+          <t>cpt_ep1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1223,32 +1163,20 @@
           <t>keyfact_recall</t>
         </is>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>0.407</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>0.386</v>
-      </c>
-      <c r="H15" s="3" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="J15" s="3" t="n">
-        <v>0.064</v>
-      </c>
-      <c r="K15" s="3" t="n">
-        <v>0.326</v>
-      </c>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="3" t="n"/>
+      <c r="K15" s="3" t="n"/>
       <c r="L15" s="2" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__ep2__bf16serve</t>
+          <t>gemma-4-e4b-it__cpt_ep1</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1258,12 +1186,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>ep2</t>
+          <t>cpt_ep1</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1272,22 +1200,22 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.014</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.018</v>
+        <v>0.004</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.054</v>
+        <v>0.011</v>
       </c>
       <c r="I16" s="3" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="J16" s="3" t="n">
         <v>0.029</v>
       </c>
-      <c r="J16" s="3" t="n">
-        <v>0.082</v>
-      </c>
       <c r="K16" s="3" t="n">
-        <v>0.001</v>
+        <v>0.257</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>279</v>
@@ -1296,7 +1224,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__ep3__bf16serve</t>
+          <t>gemma-4-e4b-it__cpt_ep1__bf16serve</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1306,7 +1234,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>ep3</t>
+          <t>cpt_ep1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1320,22 +1248,22 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.622</v>
+        <v>0.52</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.629</v>
+        <v>0.554</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-0.007</v>
+        <v>-0.034</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0.047</v>
+        <v>-0.068</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.032</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.754</v>
+        <v>0.058</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>279</v>
@@ -1344,7 +1272,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__ep3__bf16serve</t>
+          <t>gemma-4-e4b-it__cpt_ep1__bf16serve</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1354,7 +1282,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>ep3</t>
+          <t>cpt_ep1</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1368,22 +1296,22 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.423</v>
+        <v>0.322</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.402</v>
+        <v>0.317</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.021</v>
+        <v>0.006</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>-0.02</v>
+        <v>-0.027</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.063</v>
+        <v>0.04</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.319</v>
+        <v>0.75</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>279</v>
@@ -1392,7 +1320,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__ep3__bf16serve</t>
+          <t>gemma-4-e4b-it__cpt_ep1__bf16serve</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1402,7 +1330,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>ep3</t>
+          <t>cpt_ep1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1416,22 +1344,22 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0.108</v>
+        <v>0.014</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0.018</v>
+        <v>0.004</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>0.09</v>
+        <v>0.011</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.057</v>
+        <v>-0.004</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.125</v>
+        <v>0.029</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0</v>
+        <v>0.257</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>279</v>
@@ -1440,7 +1368,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__ft1run__bf16serve</t>
+          <t>gemma-4-e4b-it__ep1</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1450,12 +1378,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>ft1run</t>
+          <t>ep1</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1464,22 +1392,22 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.536</v>
+        <v>0.538</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.584</v>
+        <v>0.593</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>-0.048</v>
+        <v>-0.056</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>-0.082</v>
+        <v>-0.097</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>-0.016</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.004</v>
+        <v>0.01</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>279</v>
@@ -1488,7 +1416,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__ft1run__bf16serve</t>
+          <t>gemma-4-e4b-it__ep1</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1498,12 +1426,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>ft1run</t>
+          <t>ep1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1512,22 +1440,22 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.326</v>
+        <v>0.365</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.35</v>
+        <v>0.366</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>-0.024</v>
+        <v>-0.001</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>-0.06</v>
+        <v>-0.042</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.041</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0.158</v>
+        <v>0.967</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>279</v>
@@ -1536,7 +1464,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__ft1run__bf16serve</t>
+          <t>gemma-4-e4b-it__ep1</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1546,12 +1474,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>ft1run</t>
+          <t>ep1</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1560,22 +1488,22 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.011</v>
+        <v>0.039</v>
       </c>
       <c r="G22" s="3" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="I22" s="3" t="n">
         <v>0.004</v>
       </c>
-      <c r="H22" s="3" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="I22" s="3" t="n">
-        <v>-0.007</v>
-      </c>
       <c r="J22" s="3" t="n">
-        <v>0.022</v>
+        <v>0.043</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>0.451</v>
+        <v>0.044</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>279</v>
@@ -1584,22 +1512,22 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__base</t>
+          <t>gemma-4-e4b-it__ep1__bf16serve</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct</t>
+          <t>gemma-4-e4b-it</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ep1</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>bf16serve</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1608,22 +1536,22 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.543</v>
+        <v>0.541</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.522</v>
+        <v>0.595</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.022</v>
+        <v>-0.054</v>
       </c>
       <c r="I23" s="3" t="n">
+        <v>-0.095</v>
+      </c>
+      <c r="J23" s="3" t="n">
         <v>-0.016</v>
       </c>
-      <c r="J23" s="3" t="n">
-        <v>0.056</v>
-      </c>
       <c r="K23" s="3" t="n">
-        <v>0.286</v>
+        <v>0.006</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>279</v>
@@ -1632,22 +1560,22 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__base</t>
+          <t>gemma-4-e4b-it__ep1__bf16serve</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct</t>
+          <t>gemma-4-e4b-it</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ep1</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>bf16serve</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1656,22 +1584,22 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.508</v>
+        <v>0.362</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.498</v>
+        <v>0.359</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>0.011</v>
+        <v>0.003</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>-0.022</v>
+        <v>-0.036</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.045</v>
+        <v>0.044</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>0.536</v>
+        <v>0.873</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>279</v>
@@ -1680,22 +1608,22 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__base</t>
+          <t>gemma-4-e4b-it__ep1__bf16serve</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct</t>
+          <t>gemma-4-e4b-it</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ep1</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>bf16serve</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1704,22 +1632,22 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0</v>
+        <v>-0.011</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>1</v>
+        <v>0.415</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>279</v>
@@ -1728,17 +1656,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__concise40</t>
+          <t>gemma-4-e4b-it__ep2</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct</t>
+          <t>gemma-4-e4b-it</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>concise40</t>
+          <t>ep2</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1752,41 +1680,41 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.464</v>
+        <v>0.743</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.53</v>
+        <v>0.622</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>-0.066</v>
+        <v>0.122</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-0.104</v>
+        <v>0.077</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0.029</v>
+        <v>0.173</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__concise40</t>
+          <t>gemma-4-e4b-it__ep2</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct</t>
+          <t>gemma-4-e4b-it</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>concise40</t>
+          <t>ep2</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1800,22 +1728,22 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.368</v>
+        <v>0.61</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.356</v>
+        <v>0.414</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.012</v>
+        <v>0.196</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.027</v>
+        <v>0.145</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.051</v>
+        <v>0.244</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.548</v>
+        <v>0</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>279</v>
@@ -1824,17 +1752,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__concise40</t>
+          <t>gemma-4-e4b-it__ep2</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct</t>
+          <t>gemma-4-e4b-it</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>concise40</t>
+          <t>ep2</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1848,22 +1776,22 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.419</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>0.075</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>0.344</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.287</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>0.405</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>279</v>
@@ -1872,17 +1800,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__cpt_ep1__bf16serve</t>
+          <t>gemma-4-e4b-it__ep2__bf16serve</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct</t>
+          <t>gemma-4-e4b-it</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>cpt_ep1</t>
+          <t>ep2</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1896,41 +1824,41 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.554</v>
+        <v>0.586</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.572</v>
+        <v>0.599</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.018</v>
+        <v>-0.013</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.059</v>
+        <v>-0.054</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.02</v>
+        <v>0.029</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.383</v>
+        <v>0.597</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__cpt_ep1__bf16serve</t>
+          <t>gemma-4-e4b-it__ep2__bf16serve</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct</t>
+          <t>gemma-4-e4b-it</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>cpt_ep1</t>
+          <t>ep2</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1944,22 +1872,22 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.391</v>
+        <v>0.407</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.372</v>
+        <v>0.386</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-0.017</v>
+        <v>-0.02</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.055</v>
+        <v>0.064</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>0.271</v>
+        <v>0.326</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>279</v>
@@ -1968,17 +1896,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__cpt_ep1__bf16serve</t>
+          <t>gemma-4-e4b-it__ep2__bf16serve</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct</t>
+          <t>gemma-4-e4b-it</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>cpt_ep1</t>
+          <t>ep2</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1992,22 +1920,22 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="I31" s="3" t="n">
         <v>0.029</v>
       </c>
-      <c r="G31" s="3" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="H31" s="3" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="I31" s="3" t="n">
-        <v>0.007</v>
-      </c>
       <c r="J31" s="3" t="n">
-        <v>0.039</v>
+        <v>0.082</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.02</v>
+        <v>0.001</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>279</v>
@@ -2016,22 +1944,22 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__cpt_ep2__bf16serve</t>
+          <t>gemma-4-e4b-it__ep3</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct</t>
+          <t>gemma-4-e4b-it</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>cpt_ep2</t>
+          <t>ep3</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2040,19 +1968,19 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.735</v>
+        <v>0.828</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.62</v>
+        <v>0.613</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>0.115</v>
+        <v>0.215</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0.073</v>
+        <v>0.174</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.156</v>
+        <v>0.258</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>0</v>
@@ -2064,22 +1992,22 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__cpt_ep2__bf16serve</t>
+          <t>gemma-4-e4b-it__ep3</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct</t>
+          <t>gemma-4-e4b-it</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>cpt_ep2</t>
+          <t>ep3</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2088,19 +2016,19 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0.574</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.419</v>
+        <v>0.435</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0.155</v>
+        <v>0.247</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>0.11</v>
+        <v>0.196</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.205</v>
+        <v>0.299</v>
       </c>
       <c r="K33" s="3" t="n">
         <v>0</v>
@@ -2112,22 +2040,22 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__cpt_ep2__bf16serve</t>
+          <t>gemma-4-e4b-it__ep3</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct</t>
+          <t>gemma-4-e4b-it</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>cpt_ep2</t>
+          <t>ep3</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2136,19 +2064,19 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.323</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0.075</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0.247</v>
+        <v>0.491</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0.197</v>
+        <v>0.434</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.301</v>
+        <v>0.548</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0</v>
@@ -2160,17 +2088,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__ep1__bf16serve</t>
+          <t>gemma-4-e4b-it__ep3__bf16serve</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct</t>
+          <t>gemma-4-e4b-it</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>ep1</t>
+          <t>ep3</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2184,22 +2112,22 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.597</v>
+        <v>0.622</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.615</v>
+        <v>0.629</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>-0.018</v>
+        <v>-0.007</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>-0.063</v>
+        <v>-0.047</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.025</v>
+        <v>0.032</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>0.472</v>
+        <v>0.754</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>279</v>
@@ -2208,17 +2136,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__ep1__bf16serve</t>
+          <t>gemma-4-e4b-it__ep3__bf16serve</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct</t>
+          <t>gemma-4-e4b-it</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>ep1</t>
+          <t>ep3</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2232,22 +2160,22 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.421</v>
+        <v>0.423</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.387</v>
+        <v>0.402</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.034</v>
+        <v>0.021</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>-0.007</v>
+        <v>-0.02</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.074</v>
+        <v>0.063</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.105</v>
+        <v>0.319</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>279</v>
@@ -2256,17 +2184,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__ep1__bf16serve</t>
+          <t>gemma-4-e4b-it__ep3__bf16serve</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct</t>
+          <t>gemma-4-e4b-it</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>ep1</t>
+          <t>ep3</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2280,19 +2208,19 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.108</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.025</v>
+        <v>0.018</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0.061</v>
+        <v>0.09</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0.032</v>
+        <v>0.057</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.09</v>
+        <v>0.125</v>
       </c>
       <c r="K37" s="3" t="n">
         <v>0</v>
@@ -2304,22 +2232,22 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__ep2__bf16serve</t>
+          <t>gemma-4-e4b-it__ft1run</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct</t>
+          <t>gemma-4-e4b-it</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>ep2</t>
+          <t>ft1run</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2327,47 +2255,35 @@
           <t>judge_lenient</t>
         </is>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>0.848</v>
-      </c>
-      <c r="G38" s="3" t="n">
-        <v>0.674</v>
-      </c>
-      <c r="H38" s="3" t="n">
-        <v>0.174</v>
-      </c>
-      <c r="I38" s="3" t="n">
-        <v>0.131</v>
-      </c>
-      <c r="J38" s="3" t="n">
-        <v>0.217</v>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="F38" s="3" t="n"/>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+      <c r="I38" s="3" t="n"/>
+      <c r="J38" s="3" t="n"/>
+      <c r="K38" s="3" t="n"/>
       <c r="L38" s="2" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__ep2__bf16serve</t>
+          <t>gemma-4-e4b-it__ft1run</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct</t>
+          <t>gemma-4-e4b-it</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>ep2</t>
+          <t>ft1run</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2375,47 +2291,35 @@
           <t>keyfact_recall</t>
         </is>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>0.729</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>0.487</v>
-      </c>
-      <c r="H39" s="3" t="n">
-        <v>0.241</v>
-      </c>
-      <c r="I39" s="3" t="n">
-        <v>0.191</v>
-      </c>
-      <c r="J39" s="3" t="n">
-        <v>0.293</v>
-      </c>
-      <c r="K39" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="F39" s="3" t="n"/>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+      <c r="I39" s="3" t="n"/>
+      <c r="J39" s="3" t="n"/>
+      <c r="K39" s="3" t="n"/>
       <c r="L39" s="2" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__ep2__bf16serve</t>
+          <t>gemma-4-e4b-it__ft1run</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct</t>
+          <t>gemma-4-e4b-it</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>ep2</t>
+          <t>ft1run</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2424,22 +2328,22 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.667</v>
+        <v>0.025</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.125</v>
+        <v>0.007</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0.541</v>
+        <v>0.018</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.599</v>
+        <v>0.036</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>0.073</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>279</v>
@@ -2448,17 +2352,17 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__ep3__bf16serve</t>
+          <t>gemma-4-e4b-it__ft1run__bf16serve</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct</t>
+          <t>gemma-4-e4b-it</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>ep3</t>
+          <t>ft1run</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2472,22 +2376,22 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.889</v>
+        <v>0.536</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.654</v>
+        <v>0.584</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.235</v>
+        <v>-0.048</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.194</v>
+        <v>-0.082</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.274</v>
+        <v>-0.016</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>279</v>
@@ -2496,17 +2400,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__ep3__bf16serve</t>
+          <t>gemma-4-e4b-it__ft1run__bf16serve</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct</t>
+          <t>gemma-4-e4b-it</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>ep3</t>
+          <t>ft1run</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2520,22 +2424,22 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.758</v>
+        <v>0.326</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.485</v>
+        <v>0.35</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>0.273</v>
+        <v>-0.024</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>0.224</v>
+        <v>-0.06</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.325</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>0</v>
+        <v>0.158</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>279</v>
@@ -2544,17 +2448,17 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__ep3__bf16serve</t>
+          <t>gemma-4-e4b-it__ft1run__bf16serve</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct</t>
+          <t>gemma-4-e4b-it</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>ep3</t>
+          <t>ft1run</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2568,22 +2472,22 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.746</v>
+        <v>0.011</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.143</v>
+        <v>0.004</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>0.602</v>
+        <v>0.007</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>0.541</v>
+        <v>-0.007</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.663</v>
+        <v>0.022</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>0</v>
+        <v>0.451</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>279</v>
@@ -2592,22 +2496,22 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__ft1run__bf16serve</t>
+          <t>gemma-4-e4b-it__nf4base</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct</t>
+          <t>gemma-4-e4b-it</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>ft1run</t>
+          <t>nf4base</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2615,47 +2519,35 @@
           <t>judge_lenient</t>
         </is>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="H44" s="3" t="n">
-        <v>-0.018</v>
-      </c>
-      <c r="I44" s="3" t="n">
-        <v>-0.059</v>
-      </c>
-      <c r="J44" s="3" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K44" s="3" t="n">
-        <v>0.395</v>
-      </c>
+      <c r="F44" s="3" t="n"/>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+      <c r="I44" s="3" t="n"/>
+      <c r="J44" s="3" t="n"/>
+      <c r="K44" s="3" t="n"/>
       <c r="L44" s="2" t="n">
-        <v>278</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__ft1run__bf16serve</t>
+          <t>gemma-4-e4b-it__nf4base</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct</t>
+          <t>gemma-4-e4b-it</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>ft1run</t>
+          <t>nf4base</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2663,47 +2555,35 @@
           <t>keyfact_recall</t>
         </is>
       </c>
-      <c r="F45" s="3" t="n">
-        <v>0.368</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>0.358</v>
-      </c>
-      <c r="H45" s="3" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="I45" s="3" t="n">
-        <v>-0.027</v>
-      </c>
-      <c r="J45" s="3" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="K45" s="3" t="n">
-        <v>0.5659999999999999</v>
-      </c>
+      <c r="F45" s="3" t="n"/>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+      <c r="I45" s="3" t="n"/>
+      <c r="J45" s="3" t="n"/>
+      <c r="K45" s="3" t="n"/>
       <c r="L45" s="2" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__ft1run__bf16serve</t>
+          <t>gemma-4-e4b-it__nf4base</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct</t>
+          <t>gemma-4-e4b-it</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>ft1run</t>
+          <t>nf4base</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2712,22 +2592,22 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0.036</v>
+        <v>0</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.061</v>
+        <v>0</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.007</v>
+        <v>1</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>279</v>
@@ -2736,17 +2616,17 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__base</t>
+          <t>gemma-4-e4b-it__seed43_ep1</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b</t>
+          <t>gemma-4-e4b-it</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>seed43_ep1</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2759,42 +2639,30 @@
           <t>judge_lenient</t>
         </is>
       </c>
-      <c r="F47" s="3" t="n">
-        <v>0.647</v>
-      </c>
-      <c r="G47" s="3" t="n">
-        <v>0.649</v>
-      </c>
-      <c r="H47" s="3" t="n">
-        <v>-0.002</v>
-      </c>
-      <c r="I47" s="3" t="n">
-        <v>-0.045</v>
-      </c>
-      <c r="J47" s="3" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="K47" s="3" t="n">
-        <v>0.965</v>
-      </c>
+      <c r="F47" s="3" t="n"/>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+      <c r="I47" s="3" t="n"/>
+      <c r="J47" s="3" t="n"/>
+      <c r="K47" s="3" t="n"/>
       <c r="L47" s="2" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__base</t>
+          <t>gemma-4-e4b-it__seed43_ep1</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b</t>
+          <t>gemma-4-e4b-it</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>seed43_ep1</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -2807,42 +2675,30 @@
           <t>keyfact_recall</t>
         </is>
       </c>
-      <c r="F48" s="3" t="n">
-        <v>0.547</v>
-      </c>
-      <c r="G48" s="3" t="n">
-        <v>0.523</v>
-      </c>
-      <c r="H48" s="3" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="I48" s="3" t="n">
-        <v>-0.007</v>
-      </c>
-      <c r="J48" s="3" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="K48" s="3" t="n">
-        <v>0.14</v>
-      </c>
+      <c r="F48" s="3" t="n"/>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+      <c r="I48" s="3" t="n"/>
+      <c r="J48" s="3" t="n"/>
+      <c r="K48" s="3" t="n"/>
       <c r="L48" s="2" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__base</t>
+          <t>gemma-4-e4b-it__seed43_ep1</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b</t>
+          <t>gemma-4-e4b-it</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>seed43_ep1</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2856,22 +2712,22 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>0</v>
+        <v>0.043</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>1</v>
+        <v>0.002</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>279</v>
@@ -2880,17 +2736,17 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__concise40</t>
+          <t>llama-3.1-8b-instruct__base</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b</t>
+          <t>llama-3.1-8b-instruct</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>concise40</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2904,22 +2760,22 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
+        <v>0.543</v>
+      </c>
+      <c r="G50" s="3" t="n">
         <v>0.522</v>
       </c>
-      <c r="G50" s="3" t="n">
-        <v>0.582</v>
-      </c>
       <c r="H50" s="3" t="n">
-        <v>-0.061</v>
+        <v>0.022</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>-0.102</v>
+        <v>-0.016</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>-0.023</v>
+        <v>0.056</v>
       </c>
       <c r="K50" s="3" t="n">
-        <v>0.002</v>
+        <v>0.286</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>279</v>
@@ -2928,17 +2784,17 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__concise40</t>
+          <t>llama-3.1-8b-instruct__base</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b</t>
+          <t>llama-3.1-8b-instruct</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>concise40</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -2952,22 +2808,22 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.334</v>
+        <v>0.508</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.316</v>
+        <v>0.498</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>0.018</v>
+        <v>0.011</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>-0.014</v>
+        <v>-0.022</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.048</v>
+        <v>0.045</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>0.281</v>
+        <v>0.536</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>279</v>
@@ -2976,17 +2832,17 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__concise40</t>
+          <t>llama-3.1-8b-instruct__base</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b</t>
+          <t>llama-3.1-8b-instruct</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>concise40</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3024,22 +2880,22 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__cpt_ep1__bf16serve</t>
+          <t>llama-3.1-8b-instruct__concise40</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b</t>
+          <t>llama-3.1-8b-instruct</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>cpt_ep1</t>
+          <t>concise40</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -3048,46 +2904,46 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.464</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.575</v>
+        <v>0.53</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>-0.016</v>
+        <v>-0.066</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>-0.054</v>
+        <v>-0.104</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.02</v>
+        <v>-0.029</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>0.433</v>
+        <v>0</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__cpt_ep1__bf16serve</t>
+          <t>llama-3.1-8b-instruct__concise40</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b</t>
+          <t>llama-3.1-8b-instruct</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>cpt_ep1</t>
+          <t>concise40</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3096,22 +2952,22 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.353</v>
+        <v>0.368</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.333</v>
+        <v>0.356</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>0.02</v>
+        <v>0.012</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>-0.019</v>
+        <v>-0.027</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.059</v>
+        <v>0.051</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>0.32</v>
+        <v>0.548</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>279</v>
@@ -3120,22 +2976,22 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__cpt_ep1__bf16serve</t>
+          <t>llama-3.1-8b-instruct__concise40</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b</t>
+          <t>llama-3.1-8b-instruct</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>cpt_ep1</t>
+          <t>concise40</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3144,22 +3000,22 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.022</v>
+        <v>0</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="I55" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.036</v>
+        <v>0</v>
       </c>
       <c r="K55" s="3" t="n">
-        <v>0.08699999999999999</v>
+        <v>1</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>279</v>
@@ -3168,22 +3024,22 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__ep1__bf16serve</t>
+          <t>llama-3.1-8b-instruct__cpt_ep1</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b</t>
+          <t>llama-3.1-8b-instruct</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>ep1</t>
+          <t>cpt_ep1</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3191,47 +3047,35 @@
           <t>judge_lenient</t>
         </is>
       </c>
-      <c r="F56" s="3" t="n">
-        <v>0.5659999999999999</v>
-      </c>
-      <c r="G56" s="3" t="n">
-        <v>0.573</v>
-      </c>
-      <c r="H56" s="3" t="n">
-        <v>-0.007</v>
-      </c>
-      <c r="I56" s="3" t="n">
-        <v>-0.045</v>
-      </c>
-      <c r="J56" s="3" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="K56" s="3" t="n">
-        <v>0.758</v>
-      </c>
+      <c r="F56" s="3" t="n"/>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
+      <c r="I56" s="3" t="n"/>
+      <c r="J56" s="3" t="n"/>
+      <c r="K56" s="3" t="n"/>
       <c r="L56" s="2" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__ep1__bf16serve</t>
+          <t>llama-3.1-8b-instruct__cpt_ep1</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b</t>
+          <t>llama-3.1-8b-instruct</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>ep1</t>
+          <t>cpt_ep1</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3239,47 +3083,35 @@
           <t>keyfact_recall</t>
         </is>
       </c>
-      <c r="F57" s="3" t="n">
-        <v>0.379</v>
-      </c>
-      <c r="G57" s="3" t="n">
-        <v>0.338</v>
-      </c>
-      <c r="H57" s="3" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="I57" s="3" t="n">
-        <v>-0.001</v>
-      </c>
-      <c r="J57" s="3" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="K57" s="3" t="n">
-        <v>0.051</v>
-      </c>
+      <c r="F57" s="3" t="n"/>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
+      <c r="I57" s="3" t="n"/>
+      <c r="J57" s="3" t="n"/>
+      <c r="K57" s="3" t="n"/>
       <c r="L57" s="2" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__ep1__bf16serve</t>
+          <t>llama-3.1-8b-instruct__cpt_ep1</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b</t>
+          <t>llama-3.1-8b-instruct</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>ep1</t>
+          <t>cpt_ep1</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3288,22 +3120,22 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.057</v>
+        <v>0.047</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.011</v>
+        <v>0.018</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>0.047</v>
+        <v>0.029</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>0.022</v>
+        <v>0.007</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.054</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>279</v>
@@ -3312,17 +3144,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__ep2__bf16serve</t>
+          <t>llama-3.1-8b-instruct__cpt_ep1__bf16serve</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b</t>
+          <t>llama-3.1-8b-instruct</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>ep2</t>
+          <t>cpt_ep1</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3336,41 +3168,41 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.654</v>
+        <v>0.554</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.59</v>
+        <v>0.572</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>0.065</v>
+        <v>-0.018</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>0.022</v>
+        <v>-0.059</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.106</v>
+        <v>0.02</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>0.003</v>
+        <v>0.383</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__ep2__bf16serve</t>
+          <t>llama-3.1-8b-instruct__cpt_ep1__bf16serve</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b</t>
+          <t>llama-3.1-8b-instruct</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>ep2</t>
+          <t>cpt_ep1</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3384,22 +3216,22 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.492</v>
+        <v>0.391</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.426</v>
+        <v>0.372</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>0.066</v>
+        <v>0.02</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>0.024</v>
+        <v>-0.017</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.111</v>
+        <v>0.055</v>
       </c>
       <c r="K60" s="3" t="n">
-        <v>0.005</v>
+        <v>0.271</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>279</v>
@@ -3408,17 +3240,17 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__ep2__bf16serve</t>
+          <t>llama-3.1-8b-instruct__cpt_ep1__bf16serve</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b</t>
+          <t>llama-3.1-8b-instruct</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>ep2</t>
+          <t>cpt_ep1</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -3432,22 +3264,22 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.194</v>
+        <v>0.029</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.025</v>
+        <v>0.007</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0.168</v>
+        <v>0.022</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0.122</v>
+        <v>0.007</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.215</v>
+        <v>0.039</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>279</v>
@@ -3456,22 +3288,22 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__ep3__bf16serve</t>
+          <t>llama-3.1-8b-instruct__cpt_ep2</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b</t>
+          <t>llama-3.1-8b-instruct</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>ep3</t>
+          <t>cpt_ep2</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3479,47 +3311,35 @@
           <t>judge_lenient</t>
         </is>
       </c>
-      <c r="F62" s="3" t="n">
-        <v>0.642</v>
-      </c>
-      <c r="G62" s="3" t="n">
-        <v>0.584</v>
-      </c>
-      <c r="H62" s="3" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="I62" s="3" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="J62" s="3" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="K62" s="3" t="n">
-        <v>0.012</v>
-      </c>
+      <c r="F62" s="3" t="n"/>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+      <c r="I62" s="3" t="n"/>
+      <c r="J62" s="3" t="n"/>
+      <c r="K62" s="3" t="n"/>
       <c r="L62" s="2" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__ep3__bf16serve</t>
+          <t>llama-3.1-8b-instruct__cpt_ep2</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b</t>
+          <t>llama-3.1-8b-instruct</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>ep3</t>
+          <t>cpt_ep2</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3527,47 +3347,35 @@
           <t>keyfact_recall</t>
         </is>
       </c>
-      <c r="F63" s="3" t="n">
-        <v>0.516</v>
-      </c>
-      <c r="G63" s="3" t="n">
-        <v>0.407</v>
-      </c>
-      <c r="H63" s="3" t="n">
-        <v>0.109</v>
-      </c>
-      <c r="I63" s="3" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="J63" s="3" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="K63" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="F63" s="3" t="n"/>
+      <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n"/>
+      <c r="I63" s="3" t="n"/>
+      <c r="J63" s="3" t="n"/>
+      <c r="K63" s="3" t="n"/>
       <c r="L63" s="2" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__ep3__bf16serve</t>
+          <t>llama-3.1-8b-instruct__cpt_ep2</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b</t>
+          <t>llama-3.1-8b-instruct</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>ep3</t>
+          <t>cpt_ep2</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -3576,19 +3384,19 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.215</v>
+        <v>0.541</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.025</v>
+        <v>0.122</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0.19</v>
+        <v>0.419</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0.143</v>
+        <v>0.358</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.24</v>
+        <v>0.48</v>
       </c>
       <c r="K64" s="3" t="n">
         <v>0</v>
@@ -3600,17 +3408,17 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__ft1run__bf16serve</t>
+          <t>llama-3.1-8b-instruct__cpt_ep2__bf16serve</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b</t>
+          <t>llama-3.1-8b-instruct</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>ft1run</t>
+          <t>cpt_ep2</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -3624,22 +3432,22 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>0.534</v>
+        <v>0.735</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>-0.027</v>
+        <v>0.115</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>-0.066</v>
+        <v>0.073</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.011</v>
+        <v>0.156</v>
       </c>
       <c r="K65" s="3" t="n">
-        <v>0.189</v>
+        <v>0</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>279</v>
@@ -3648,17 +3456,17 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__ft1run__bf16serve</t>
+          <t>llama-3.1-8b-instruct__cpt_ep2__bf16serve</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b</t>
+          <t>llama-3.1-8b-instruct</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>ft1run</t>
+          <t>cpt_ep2</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -3672,22 +3480,22 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.35</v>
+        <v>0.574</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.352</v>
+        <v>0.419</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>-0.002</v>
+        <v>0.155</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>-0.041</v>
+        <v>0.11</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.036</v>
+        <v>0.205</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>0.905</v>
+        <v>0</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>279</v>
@@ -3696,48 +3504,3336 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>llama-3.1-8b-instruct__cpt_ep2__bf16serve</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>cpt_ep2</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>bf16serve</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>exact_repro</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="H67" s="3" t="n">
+        <v>0.247</v>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="J67" s="3" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="K67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct__ep1</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>ep1</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>judge_lenient</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="I68" s="3" t="n">
+        <v>-0.029</v>
+      </c>
+      <c r="J68" s="3" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="K68" s="3" t="n">
+        <v>0.507</v>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct__ep1</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>ep1</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>keyfact_recall</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>0.448</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="H69" s="3" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="I69" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J69" s="3" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="K69" s="3" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct__ep1</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>ep1</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>exact_repro</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="H70" s="3" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="I70" s="3" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="J70" s="3" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="K70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct__ep1__bf16serve</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>ep1</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>bf16serve</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>judge_lenient</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="H71" s="3" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="I71" s="3" t="n">
+        <v>-0.063</v>
+      </c>
+      <c r="J71" s="3" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="K71" s="3" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct__ep1__bf16serve</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>ep1</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>bf16serve</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>keyfact_recall</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>0.421</v>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="H72" s="3" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="I72" s="3" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="J72" s="3" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="K72" s="3" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="L72" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct__ep1__bf16serve</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>ep1</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>bf16serve</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>exact_repro</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="H73" s="3" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="I73" s="3" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="J73" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct__ep2</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>ep2</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>judge_lenient</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>0.962</v>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="H74" s="3" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="I74" s="3" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="J74" s="3" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="K74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct__ep2</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>ep2</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>keyfact_recall</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>0.544</v>
+      </c>
+      <c r="H75" s="3" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="I75" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J75" s="3" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="K75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct__ep2</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>ep2</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>exact_repro</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="H76" s="3" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="I76" s="3" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="J76" s="3" t="n">
+        <v>0.703</v>
+      </c>
+      <c r="K76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct__ep2__bf16serve</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>ep2</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>bf16serve</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>judge_lenient</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>0.674</v>
+      </c>
+      <c r="H77" s="3" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="I77" s="3" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="J77" s="3" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="K77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct__ep2__bf16serve</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>ep2</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>bf16serve</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>keyfact_recall</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>0.487</v>
+      </c>
+      <c r="H78" s="3" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="I78" s="3" t="n">
+        <v>0.191</v>
+      </c>
+      <c r="J78" s="3" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="K78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct__ep2__bf16serve</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>ep2</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>bf16serve</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>exact_repro</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="H79" s="3" t="n">
+        <v>0.541</v>
+      </c>
+      <c r="I79" s="3" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="J79" s="3" t="n">
+        <v>0.599</v>
+      </c>
+      <c r="K79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct__ep3</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>ep3</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>judge_lenient</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>0.986</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="J80" s="3" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="K80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct__ep3</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>ep3</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>keyfact_recall</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="H81" s="3" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="I81" s="3" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="J81" s="3" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="K81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct__ep3</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>ep3</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>exact_repro</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="H82" s="3" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="I82" s="3" t="n">
+        <v>0.627</v>
+      </c>
+      <c r="J82" s="3" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="K82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct__ep3__bf16serve</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>ep3</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>bf16serve</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>judge_lenient</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>0.654</v>
+      </c>
+      <c r="H83" s="3" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="I83" s="3" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="J83" s="3" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="K83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct__ep3__bf16serve</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>ep3</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>bf16serve</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>keyfact_recall</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="H84" s="3" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="I84" s="3" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="J84" s="3" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="K84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct__ep3__bf16serve</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>ep3</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>bf16serve</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>exact_repro</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="H85" s="3" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="I85" s="3" t="n">
+        <v>0.541</v>
+      </c>
+      <c r="J85" s="3" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="K85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct__ft1run</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>ft1run</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>judge_lenient</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="n"/>
+      <c r="G86" s="3" t="n"/>
+      <c r="H86" s="3" t="n"/>
+      <c r="I86" s="3" t="n"/>
+      <c r="J86" s="3" t="n"/>
+      <c r="K86" s="3" t="n"/>
+      <c r="L86" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct__ft1run</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>ft1run</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>keyfact_recall</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="n"/>
+      <c r="G87" s="3" t="n"/>
+      <c r="H87" s="3" t="n"/>
+      <c r="I87" s="3" t="n"/>
+      <c r="J87" s="3" t="n"/>
+      <c r="K87" s="3" t="n"/>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct__ft1run</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>ft1run</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>exact_repro</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="H88" s="3" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="I88" s="3" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="J88" s="3" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="K88" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct__ft1run__bf16serve</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>ft1run</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>bf16serve</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>judge_lenient</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="I89" s="3" t="n">
+        <v>-0.059</v>
+      </c>
+      <c r="J89" s="3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K89" s="3" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct__ft1run__bf16serve</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>ft1run</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>bf16serve</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>keyfact_recall</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="H90" s="3" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="I90" s="3" t="n">
+        <v>-0.027</v>
+      </c>
+      <c r="J90" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K90" s="3" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct__ft1run__bf16serve</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>ft1run</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>bf16serve</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>exact_repro</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="H91" s="3" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="I91" s="3" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="J91" s="3" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="K91" s="3" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct__nf4base</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>nf4base</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>judge_lenient</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="n"/>
+      <c r="G92" s="3" t="n"/>
+      <c r="H92" s="3" t="n"/>
+      <c r="I92" s="3" t="n"/>
+      <c r="J92" s="3" t="n"/>
+      <c r="K92" s="3" t="n"/>
+      <c r="L92" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct__nf4base</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>nf4base</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>keyfact_recall</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="n"/>
+      <c r="G93" s="3" t="n"/>
+      <c r="H93" s="3" t="n"/>
+      <c r="I93" s="3" t="n"/>
+      <c r="J93" s="3" t="n"/>
+      <c r="K93" s="3" t="n"/>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct__nf4base</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>nf4base</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>exact_repro</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct__seed43_ep1</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>seed43_ep1</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>judge_lenient</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="n"/>
+      <c r="G95" s="3" t="n"/>
+      <c r="H95" s="3" t="n"/>
+      <c r="I95" s="3" t="n"/>
+      <c r="J95" s="3" t="n"/>
+      <c r="K95" s="3" t="n"/>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct__seed43_ep1</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>seed43_ep1</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>keyfact_recall</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="n"/>
+      <c r="G96" s="3" t="n"/>
+      <c r="H96" s="3" t="n"/>
+      <c r="I96" s="3" t="n"/>
+      <c r="J96" s="3" t="n"/>
+      <c r="K96" s="3" t="n"/>
+      <c r="L96" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct__seed43_ep1</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>llama-3.1-8b-instruct</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>seed43_ep1</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>exact_repro</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="G97" s="3" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="H97" s="3" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="J97" s="3" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="K97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__base</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>judge_lenient</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="G98" s="3" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="H98" s="3" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="I98" s="3" t="n">
+        <v>-0.045</v>
+      </c>
+      <c r="J98" s="3" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="K98" s="3" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__base</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>keyfact_recall</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>0.547</v>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="H99" s="3" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="I99" s="3" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="J99" s="3" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="K99" s="3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__base</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>exact_repro</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__concise40</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>concise40</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>judge_lenient</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>0.522</v>
+      </c>
+      <c r="G101" s="3" t="n">
+        <v>0.582</v>
+      </c>
+      <c r="H101" s="3" t="n">
+        <v>-0.061</v>
+      </c>
+      <c r="I101" s="3" t="n">
+        <v>-0.102</v>
+      </c>
+      <c r="J101" s="3" t="n">
+        <v>-0.023</v>
+      </c>
+      <c r="K101" s="3" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__concise40</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>concise40</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>keyfact_recall</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="G102" s="3" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="H102" s="3" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="I102" s="3" t="n">
+        <v>-0.014</v>
+      </c>
+      <c r="J102" s="3" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="K102" s="3" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__concise40</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>concise40</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>exact_repro</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__cpt_ep1</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>cpt_ep1</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>judge_lenient</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="n"/>
+      <c r="G104" s="3" t="n"/>
+      <c r="H104" s="3" t="n"/>
+      <c r="I104" s="3" t="n"/>
+      <c r="J104" s="3" t="n"/>
+      <c r="K104" s="3" t="n"/>
+      <c r="L104" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__cpt_ep1</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>cpt_ep1</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>keyfact_recall</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="n"/>
+      <c r="G105" s="3" t="n"/>
+      <c r="H105" s="3" t="n"/>
+      <c r="I105" s="3" t="n"/>
+      <c r="J105" s="3" t="n"/>
+      <c r="K105" s="3" t="n"/>
+      <c r="L105" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__cpt_ep1</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>cpt_ep1</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>exact_repro</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="G106" s="3" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="H106" s="3" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="I106" s="3" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="J106" s="3" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="K106" s="3" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__cpt_ep1__bf16serve</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>cpt_ep1</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>bf16serve</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>judge_lenient</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>0.5590000000000001</v>
+      </c>
+      <c r="G107" s="3" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="H107" s="3" t="n">
+        <v>-0.016</v>
+      </c>
+      <c r="I107" s="3" t="n">
+        <v>-0.054</v>
+      </c>
+      <c r="J107" s="3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K107" s="3" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__cpt_ep1__bf16serve</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>cpt_ep1</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>bf16serve</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>keyfact_recall</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="G108" s="3" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="H108" s="3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I108" s="3" t="n">
+        <v>-0.019</v>
+      </c>
+      <c r="J108" s="3" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="K108" s="3" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__cpt_ep1__bf16serve</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>cpt_ep1</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>bf16serve</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>exact_repro</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="G109" s="3" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="H109" s="3" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="I109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" s="3" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="K109" s="3" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__ep1</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>ep1</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>judge_lenient</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G110" s="3" t="n">
+        <v>0.599</v>
+      </c>
+      <c r="H110" s="3" t="n">
+        <v>-0.029</v>
+      </c>
+      <c r="I110" s="3" t="n">
+        <v>-0.068</v>
+      </c>
+      <c r="J110" s="3" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="K110" s="3" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__ep1</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>ep1</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>keyfact_recall</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="G111" s="3" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="H111" s="3" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="I111" s="3" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="J111" s="3" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="K111" s="3" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__ep1</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>ep1</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>exact_repro</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="G112" s="3" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="H112" s="3" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="I112" s="3" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="J112" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__ep1__bf16serve</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>ep1</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>bf16serve</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>judge_lenient</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="G113" s="3" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="H113" s="3" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="I113" s="3" t="n">
+        <v>-0.045</v>
+      </c>
+      <c r="J113" s="3" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="K113" s="3" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__ep1__bf16serve</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>ep1</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>bf16serve</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>keyfact_recall</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="G114" s="3" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="H114" s="3" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="I114" s="3" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="J114" s="3" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="K114" s="3" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__ep1__bf16serve</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>ep1</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>bf16serve</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>exact_repro</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="G115" s="3" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="H115" s="3" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="I115" s="3" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="J115" s="3" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="K115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__ep2</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>ep2</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>judge_lenient</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="G116" s="3" t="n">
+        <v>0.627</v>
+      </c>
+      <c r="H116" s="3" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="I116" s="3" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="J116" s="3" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="K116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__ep2</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>ep2</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>keyfact_recall</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>0.654</v>
+      </c>
+      <c r="G117" s="3" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="H117" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I117" s="3" t="n">
+        <v>0.201</v>
+      </c>
+      <c r="J117" s="3" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="K117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__ep2</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>ep2</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>exact_repro</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="H118" s="3" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="I118" s="3" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="J118" s="3" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="K118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__ep2__bf16serve</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>ep2</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>bf16serve</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>judge_lenient</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="n">
+        <v>0.654</v>
+      </c>
+      <c r="G119" s="3" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H119" s="3" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="I119" s="3" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="J119" s="3" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="K119" s="3" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__ep2__bf16serve</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>ep2</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>bf16serve</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>keyfact_recall</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="n">
+        <v>0.492</v>
+      </c>
+      <c r="G120" s="3" t="n">
+        <v>0.426</v>
+      </c>
+      <c r="H120" s="3" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="I120" s="3" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="J120" s="3" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="K120" s="3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__ep2__bf16serve</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>ep2</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>bf16serve</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>exact_repro</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="G121" s="3" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="H121" s="3" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="I121" s="3" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="J121" s="3" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="K121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__ep3</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>ep3</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>judge_lenient</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="G122" s="3" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="H122" s="3" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="I122" s="3" t="n">
+        <v>0.164</v>
+      </c>
+      <c r="J122" s="3" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="K122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__ep3</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>ep3</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>keyfact_recall</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="n">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="G123" s="3" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="H123" s="3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I123" s="3" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="J123" s="3" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="K123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__ep3</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>ep3</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>exact_repro</t>
+        </is>
+      </c>
+      <c r="F124" s="3" t="n">
+        <v>0.606</v>
+      </c>
+      <c r="G124" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H124" s="3" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="I124" s="3" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="J124" s="3" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="K124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__ep3__bf16serve</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>ep3</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>bf16serve</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>judge_lenient</t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="n">
+        <v>0.642</v>
+      </c>
+      <c r="G125" s="3" t="n">
+        <v>0.584</v>
+      </c>
+      <c r="H125" s="3" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="I125" s="3" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="J125" s="3" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="K125" s="3" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__ep3__bf16serve</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>ep3</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>bf16serve</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>keyfact_recall</t>
+        </is>
+      </c>
+      <c r="F126" s="3" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="G126" s="3" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="H126" s="3" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="I126" s="3" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="J126" s="3" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="K126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__ep3__bf16serve</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>ep3</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>bf16serve</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>exact_repro</t>
+        </is>
+      </c>
+      <c r="F127" s="3" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="G127" s="3" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="H127" s="3" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="I127" s="3" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="J127" s="3" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="K127" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__ft1run</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>ft1run</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>judge_lenient</t>
+        </is>
+      </c>
+      <c r="F128" s="3" t="n"/>
+      <c r="G128" s="3" t="n"/>
+      <c r="H128" s="3" t="n"/>
+      <c r="I128" s="3" t="n"/>
+      <c r="J128" s="3" t="n"/>
+      <c r="K128" s="3" t="n"/>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__ft1run</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>ft1run</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>keyfact_recall</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="n"/>
+      <c r="G129" s="3" t="n"/>
+      <c r="H129" s="3" t="n"/>
+      <c r="I129" s="3" t="n"/>
+      <c r="J129" s="3" t="n"/>
+      <c r="K129" s="3" t="n"/>
+      <c r="L129" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__ft1run</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>ft1run</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>exact_repro</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G130" s="3" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="H130" s="3" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="I130" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" s="3" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="K130" s="3" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="L130" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
           <t>qwen3-8b__ft1run__bf16serve</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
         <is>
           <t>qwen3-8b</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C131" s="2" t="inlineStr">
         <is>
           <t>ft1run</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>bf16serve</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>judge_lenient</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="n">
+        <v>0.534</v>
+      </c>
+      <c r="G131" s="3" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="H131" s="3" t="n">
+        <v>-0.027</v>
+      </c>
+      <c r="I131" s="3" t="n">
+        <v>-0.066</v>
+      </c>
+      <c r="J131" s="3" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="K131" s="3" t="n">
+        <v>0.189</v>
+      </c>
+      <c r="L131" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__ft1run__bf16serve</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>ft1run</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>bf16serve</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>keyfact_recall</t>
+        </is>
+      </c>
+      <c r="F132" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G132" s="3" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="H132" s="3" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="I132" s="3" t="n">
+        <v>-0.041</v>
+      </c>
+      <c r="J132" s="3" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="K132" s="3" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="L132" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__ft1run__bf16serve</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>ft1run</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>bf16serve</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>exact_repro</t>
         </is>
       </c>
-      <c r="F67" s="3" t="n">
+      <c r="F133" s="3" t="n">
         <v>0.018</v>
       </c>
-      <c r="G67" s="3" t="n">
+      <c r="G133" s="3" t="n">
         <v>0.011</v>
       </c>
-      <c r="H67" s="3" t="n">
+      <c r="H133" s="3" t="n">
         <v>0.007</v>
       </c>
-      <c r="I67" s="3" t="n">
+      <c r="I133" s="3" t="n">
         <v>-0.011</v>
       </c>
-      <c r="J67" s="3" t="n">
+      <c r="J133" s="3" t="n">
         <v>0.025</v>
       </c>
-      <c r="K67" s="3" t="n">
+      <c r="K133" s="3" t="n">
         <v>0.522</v>
       </c>
-      <c r="L67" s="2" t="n">
+      <c r="L133" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__nf4base</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>nf4base</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>judge_lenient</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="n"/>
+      <c r="G134" s="3" t="n"/>
+      <c r="H134" s="3" t="n"/>
+      <c r="I134" s="3" t="n"/>
+      <c r="J134" s="3" t="n"/>
+      <c r="K134" s="3" t="n"/>
+      <c r="L134" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__nf4base</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>nf4base</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>keyfact_recall</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="n"/>
+      <c r="G135" s="3" t="n"/>
+      <c r="H135" s="3" t="n"/>
+      <c r="I135" s="3" t="n"/>
+      <c r="J135" s="3" t="n"/>
+      <c r="K135" s="3" t="n"/>
+      <c r="L135" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__nf4base</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>nf4base</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>exact_repro</t>
+        </is>
+      </c>
+      <c r="F136" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L136" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__seed43_ep1</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>seed43_ep1</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>judge_lenient</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="n"/>
+      <c r="G137" s="3" t="n"/>
+      <c r="H137" s="3" t="n"/>
+      <c r="I137" s="3" t="n"/>
+      <c r="J137" s="3" t="n"/>
+      <c r="K137" s="3" t="n"/>
+      <c r="L137" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__seed43_ep1</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>seed43_ep1</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>keyfact_recall</t>
+        </is>
+      </c>
+      <c r="F138" s="3" t="n"/>
+      <c r="G138" s="3" t="n"/>
+      <c r="H138" s="3" t="n"/>
+      <c r="I138" s="3" t="n"/>
+      <c r="J138" s="3" t="n"/>
+      <c r="K138" s="3" t="n"/>
+      <c r="L138" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__seed43_ep1</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>seed43_ep1</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>exact_repro</t>
+        </is>
+      </c>
+      <c r="F139" s="3" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="G139" s="3" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="H139" s="3" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="I139" s="3" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="J139" s="3" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="K139" s="3" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="L139" s="2" t="n">
         <v>279</v>
       </c>
     </row>

--- a/research_materials/03_results/robustness_gap.xlsx
+++ b/research_materials/03_results/robustness_gap.xlsx
@@ -459,7 +459,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Built: 2026-10-06 23:35 by src/build_research_materials.py</t>
+          <t>Built: 2026-10-07 02:02 by src/build_research_materials.py</t>
         </is>
       </c>
     </row>
@@ -743,14 +743,26 @@
           <t>judge_lenient</t>
         </is>
       </c>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="3" t="n"/>
-      <c r="K5" s="3" t="n"/>
+      <c r="F5" s="3" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>-0.045</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0.8169999999999999</v>
+      </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>277</v>
       </c>
     </row>
     <row r="6">
@@ -779,14 +791,26 @@
           <t>keyfact_recall</t>
         </is>
       </c>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3" t="n"/>
-      <c r="J6" s="3" t="n"/>
-      <c r="K6" s="3" t="n"/>
+      <c r="F6" s="3" t="n">
+        <v>0.539</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0.549</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>-0.042</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0.5570000000000001</v>
+      </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
     </row>
     <row r="7">
@@ -1007,14 +1031,26 @@
           <t>judge_lenient</t>
         </is>
       </c>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="n"/>
-      <c r="H11" s="3" t="n"/>
-      <c r="I11" s="3" t="n"/>
-      <c r="J11" s="3" t="n"/>
-      <c r="K11" s="3" t="n"/>
+      <c r="F11" s="3" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>-0.036</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>0.057</v>
+      </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
     </row>
     <row r="12">
@@ -1043,14 +1079,26 @@
           <t>keyfact_recall</t>
         </is>
       </c>
-      <c r="F12" s="3" t="n"/>
-      <c r="G12" s="3" t="n"/>
-      <c r="H12" s="3" t="n"/>
-      <c r="I12" s="3" t="n"/>
-      <c r="J12" s="3" t="n"/>
-      <c r="K12" s="3" t="n"/>
+      <c r="F12" s="3" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>-0.028</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>0.789</v>
+      </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13">
@@ -1127,14 +1175,26 @@
           <t>judge_lenient</t>
         </is>
       </c>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3" t="n"/>
-      <c r="I14" s="3" t="n"/>
-      <c r="J14" s="3" t="n"/>
-      <c r="K14" s="3" t="n"/>
+      <c r="F14" s="3" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0.547</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>-0.045</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>-0.081</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>0.021</v>
+      </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15">
@@ -1163,14 +1223,26 @@
           <t>keyfact_recall</t>
         </is>
       </c>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3" t="n"/>
-      <c r="I15" s="3" t="n"/>
-      <c r="J15" s="3" t="n"/>
-      <c r="K15" s="3" t="n"/>
+      <c r="F15" s="3" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>0.864</v>
+      </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16">
@@ -2255,14 +2327,26 @@
           <t>judge_lenient</t>
         </is>
       </c>
-      <c r="F38" s="3" t="n"/>
-      <c r="G38" s="3" t="n"/>
-      <c r="H38" s="3" t="n"/>
-      <c r="I38" s="3" t="n"/>
-      <c r="J38" s="3" t="n"/>
-      <c r="K38" s="3" t="n"/>
+      <c r="F38" s="3" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>-0.027</v>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v>-0.065</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>0.18</v>
+      </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
     </row>
     <row r="39">
@@ -2291,14 +2375,26 @@
           <t>keyfact_recall</t>
         </is>
       </c>
-      <c r="F39" s="3" t="n"/>
-      <c r="G39" s="3" t="n"/>
-      <c r="H39" s="3" t="n"/>
-      <c r="I39" s="3" t="n"/>
-      <c r="J39" s="3" t="n"/>
-      <c r="K39" s="3" t="n"/>
+      <c r="F39" s="3" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="J39" s="3" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>0.971</v>
+      </c>
       <c r="L39" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
     </row>
     <row r="40">
@@ -2519,14 +2615,26 @@
           <t>judge_lenient</t>
         </is>
       </c>
-      <c r="F44" s="3" t="n"/>
-      <c r="G44" s="3" t="n"/>
-      <c r="H44" s="3" t="n"/>
-      <c r="I44" s="3" t="n"/>
-      <c r="J44" s="3" t="n"/>
-      <c r="K44" s="3" t="n"/>
+      <c r="F44" s="3" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>-0.043</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="K44" s="3" t="n">
+        <v>0.822</v>
+      </c>
       <c r="L44" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
     </row>
     <row r="45">
@@ -2555,14 +2663,26 @@
           <t>keyfact_recall</t>
         </is>
       </c>
-      <c r="F45" s="3" t="n"/>
-      <c r="G45" s="3" t="n"/>
-      <c r="H45" s="3" t="n"/>
-      <c r="I45" s="3" t="n"/>
-      <c r="J45" s="3" t="n"/>
-      <c r="K45" s="3" t="n"/>
+      <c r="F45" s="3" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="I45" s="3" t="n">
+        <v>-0.029</v>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>0.835</v>
+      </c>
       <c r="L45" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
     </row>
     <row r="46">
@@ -2639,14 +2759,26 @@
           <t>judge_lenient</t>
         </is>
       </c>
-      <c r="F47" s="3" t="n"/>
-      <c r="G47" s="3" t="n"/>
-      <c r="H47" s="3" t="n"/>
-      <c r="I47" s="3" t="n"/>
-      <c r="J47" s="3" t="n"/>
-      <c r="K47" s="3" t="n"/>
+      <c r="F47" s="3" t="n">
+        <v>0.543</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="H47" s="3" t="n">
+        <v>-0.014</v>
+      </c>
+      <c r="I47" s="3" t="n">
+        <v>-0.054</v>
+      </c>
+      <c r="J47" s="3" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="K47" s="3" t="n">
+        <v>0.495</v>
+      </c>
       <c r="L47" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
     </row>
     <row r="48">
@@ -2675,14 +2807,26 @@
           <t>keyfact_recall</t>
         </is>
       </c>
-      <c r="F48" s="3" t="n"/>
-      <c r="G48" s="3" t="n"/>
-      <c r="H48" s="3" t="n"/>
-      <c r="I48" s="3" t="n"/>
-      <c r="J48" s="3" t="n"/>
-      <c r="K48" s="3" t="n"/>
+      <c r="F48" s="3" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="H48" s="3" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="I48" s="3" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="J48" s="3" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="K48" s="3" t="n">
+        <v>0.115</v>
+      </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
     </row>
     <row r="49">
@@ -3047,14 +3191,26 @@
           <t>judge_lenient</t>
         </is>
       </c>
-      <c r="F56" s="3" t="n"/>
-      <c r="G56" s="3" t="n"/>
-      <c r="H56" s="3" t="n"/>
-      <c r="I56" s="3" t="n"/>
-      <c r="J56" s="3" t="n"/>
-      <c r="K56" s="3" t="n"/>
+      <c r="F56" s="3" t="n">
+        <v>0.5590000000000001</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="H56" s="3" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="I56" s="3" t="n">
+        <v>-0.041</v>
+      </c>
+      <c r="J56" s="3" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="K56" s="3" t="n">
+        <v>0.968</v>
+      </c>
       <c r="L56" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
     </row>
     <row r="57">
@@ -3083,14 +3239,26 @@
           <t>keyfact_recall</t>
         </is>
       </c>
-      <c r="F57" s="3" t="n"/>
-      <c r="G57" s="3" t="n"/>
-      <c r="H57" s="3" t="n"/>
-      <c r="I57" s="3" t="n"/>
-      <c r="J57" s="3" t="n"/>
-      <c r="K57" s="3" t="n"/>
+      <c r="F57" s="3" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="H57" s="3" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="I57" s="3" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="J57" s="3" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="K57" s="3" t="n">
+        <v>0.022</v>
+      </c>
       <c r="L57" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
     </row>
     <row r="58">
@@ -3311,14 +3479,26 @@
           <t>judge_lenient</t>
         </is>
       </c>
-      <c r="F62" s="3" t="n"/>
-      <c r="G62" s="3" t="n"/>
-      <c r="H62" s="3" t="n"/>
-      <c r="I62" s="3" t="n"/>
-      <c r="J62" s="3" t="n"/>
-      <c r="K62" s="3" t="n"/>
+      <c r="F62" s="3" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="I62" s="3" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="J62" s="3" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="K62" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="L62" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
     </row>
     <row r="63">
@@ -3347,14 +3527,26 @@
           <t>keyfact_recall</t>
         </is>
       </c>
-      <c r="F63" s="3" t="n"/>
-      <c r="G63" s="3" t="n"/>
-      <c r="H63" s="3" t="n"/>
-      <c r="I63" s="3" t="n"/>
-      <c r="J63" s="3" t="n"/>
-      <c r="K63" s="3" t="n"/>
+      <c r="F63" s="3" t="n">
+        <v>0.662</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="H63" s="3" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="I63" s="3" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="J63" s="3" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="K63" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="L63" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
     </row>
     <row r="64">
@@ -4439,14 +4631,26 @@
           <t>judge_lenient</t>
         </is>
       </c>
-      <c r="F86" s="3" t="n"/>
-      <c r="G86" s="3" t="n"/>
-      <c r="H86" s="3" t="n"/>
-      <c r="I86" s="3" t="n"/>
-      <c r="J86" s="3" t="n"/>
-      <c r="K86" s="3" t="n"/>
+      <c r="F86" s="3" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>-0.027</v>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v>-0.068</v>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="K86" s="3" t="n">
+        <v>0.209</v>
+      </c>
       <c r="L86" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
     </row>
     <row r="87">
@@ -4475,14 +4679,26 @@
           <t>keyfact_recall</t>
         </is>
       </c>
-      <c r="F87" s="3" t="n"/>
-      <c r="G87" s="3" t="n"/>
-      <c r="H87" s="3" t="n"/>
-      <c r="I87" s="3" t="n"/>
-      <c r="J87" s="3" t="n"/>
-      <c r="K87" s="3" t="n"/>
+      <c r="F87" s="3" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>-0.039</v>
+      </c>
+      <c r="J87" s="3" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="K87" s="3" t="n">
+        <v>0.964</v>
+      </c>
       <c r="L87" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
     </row>
     <row r="88">
@@ -4703,14 +4919,26 @@
           <t>judge_lenient</t>
         </is>
       </c>
-      <c r="F92" s="3" t="n"/>
-      <c r="G92" s="3" t="n"/>
-      <c r="H92" s="3" t="n"/>
-      <c r="I92" s="3" t="n"/>
-      <c r="J92" s="3" t="n"/>
-      <c r="K92" s="3" t="n"/>
+      <c r="F92" s="3" t="n">
+        <v>0.541</v>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="H92" s="3" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="I92" s="3" t="n">
+        <v>-0.052</v>
+      </c>
+      <c r="J92" s="3" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="K92" s="3" t="n">
+        <v>0.552</v>
+      </c>
       <c r="L92" s="2" t="n">
-        <v>0</v>
+        <v>278</v>
       </c>
     </row>
     <row r="93">
@@ -4739,14 +4967,26 @@
           <t>keyfact_recall</t>
         </is>
       </c>
-      <c r="F93" s="3" t="n"/>
-      <c r="G93" s="3" t="n"/>
-      <c r="H93" s="3" t="n"/>
-      <c r="I93" s="3" t="n"/>
-      <c r="J93" s="3" t="n"/>
-      <c r="K93" s="3" t="n"/>
+      <c r="F93" s="3" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="G93" s="3" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="H93" s="3" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="I93" s="3" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="J93" s="3" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="K93" s="3" t="n">
+        <v>0.141</v>
+      </c>
       <c r="L93" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
     </row>
     <row r="94">
@@ -4823,14 +5063,26 @@
           <t>judge_lenient</t>
         </is>
       </c>
-      <c r="F95" s="3" t="n"/>
-      <c r="G95" s="3" t="n"/>
-      <c r="H95" s="3" t="n"/>
-      <c r="I95" s="3" t="n"/>
-      <c r="J95" s="3" t="n"/>
-      <c r="K95" s="3" t="n"/>
+      <c r="F95" s="3" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="G95" s="3" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="H95" s="3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I95" s="3" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="J95" s="3" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="K95" s="3" t="n">
+        <v>0.369</v>
+      </c>
       <c r="L95" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
     </row>
     <row r="96">
@@ -4859,14 +5111,26 @@
           <t>keyfact_recall</t>
         </is>
       </c>
-      <c r="F96" s="3" t="n"/>
-      <c r="G96" s="3" t="n"/>
-      <c r="H96" s="3" t="n"/>
-      <c r="I96" s="3" t="n"/>
-      <c r="J96" s="3" t="n"/>
-      <c r="K96" s="3" t="n"/>
+      <c r="F96" s="3" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="G96" s="3" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="H96" s="3" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="J96" s="3" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="K96" s="3" t="n">
+        <v>0.011</v>
+      </c>
       <c r="L96" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
     </row>
     <row r="97">
@@ -5231,14 +5495,26 @@
           <t>judge_lenient</t>
         </is>
       </c>
-      <c r="F104" s="3" t="n"/>
-      <c r="G104" s="3" t="n"/>
-      <c r="H104" s="3" t="n"/>
-      <c r="I104" s="3" t="n"/>
-      <c r="J104" s="3" t="n"/>
-      <c r="K104" s="3" t="n"/>
+      <c r="F104" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G104" s="3" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="H104" s="3" t="n">
+        <v>-0.016</v>
+      </c>
+      <c r="I104" s="3" t="n">
+        <v>-0.054</v>
+      </c>
+      <c r="J104" s="3" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="K104" s="3" t="n">
+        <v>0.431</v>
+      </c>
       <c r="L104" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
     </row>
     <row r="105">
@@ -5267,14 +5543,26 @@
           <t>keyfact_recall</t>
         </is>
       </c>
-      <c r="F105" s="3" t="n"/>
-      <c r="G105" s="3" t="n"/>
-      <c r="H105" s="3" t="n"/>
-      <c r="I105" s="3" t="n"/>
-      <c r="J105" s="3" t="n"/>
-      <c r="K105" s="3" t="n"/>
+      <c r="F105" s="3" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="G105" s="3" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="H105" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I105" s="3" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="J105" s="3" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="K105" s="3" t="n">
+        <v>0.579</v>
+      </c>
       <c r="L105" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
     </row>
     <row r="106">
@@ -6359,14 +6647,26 @@
           <t>judge_lenient</t>
         </is>
       </c>
-      <c r="F128" s="3" t="n"/>
-      <c r="G128" s="3" t="n"/>
-      <c r="H128" s="3" t="n"/>
-      <c r="I128" s="3" t="n"/>
-      <c r="J128" s="3" t="n"/>
-      <c r="K128" s="3" t="n"/>
+      <c r="F128" s="3" t="n">
+        <v>0.543</v>
+      </c>
+      <c r="G128" s="3" t="n">
+        <v>0.543</v>
+      </c>
+      <c r="H128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" s="3" t="n">
+        <v>-0.038</v>
+      </c>
+      <c r="J128" s="3" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="K128" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="L128" s="2" t="n">
-        <v>0</v>
+        <v>278</v>
       </c>
     </row>
     <row r="129">
@@ -6395,14 +6695,26 @@
           <t>keyfact_recall</t>
         </is>
       </c>
-      <c r="F129" s="3" t="n"/>
-      <c r="G129" s="3" t="n"/>
-      <c r="H129" s="3" t="n"/>
-      <c r="I129" s="3" t="n"/>
-      <c r="J129" s="3" t="n"/>
-      <c r="K129" s="3" t="n"/>
+      <c r="F129" s="3" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="G129" s="3" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="H129" s="3" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="I129" s="3" t="n">
+        <v>-0.021</v>
+      </c>
+      <c r="J129" s="3" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="K129" s="3" t="n">
+        <v>0.359</v>
+      </c>
       <c r="L129" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
     </row>
     <row r="130">
@@ -6623,14 +6935,26 @@
           <t>judge_lenient</t>
         </is>
       </c>
-      <c r="F134" s="3" t="n"/>
-      <c r="G134" s="3" t="n"/>
-      <c r="H134" s="3" t="n"/>
-      <c r="I134" s="3" t="n"/>
-      <c r="J134" s="3" t="n"/>
-      <c r="K134" s="3" t="n"/>
+      <c r="F134" s="3" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="G134" s="3" t="n">
+        <v>0.658</v>
+      </c>
+      <c r="H134" s="3" t="n">
+        <v>-0.027</v>
+      </c>
+      <c r="I134" s="3" t="n">
+        <v>-0.065</v>
+      </c>
+      <c r="J134" s="3" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="K134" s="3" t="n">
+        <v>0.167</v>
+      </c>
       <c r="L134" s="2" t="n">
-        <v>0</v>
+        <v>278</v>
       </c>
     </row>
     <row r="135">
@@ -6659,14 +6983,26 @@
           <t>keyfact_recall</t>
         </is>
       </c>
-      <c r="F135" s="3" t="n"/>
-      <c r="G135" s="3" t="n"/>
-      <c r="H135" s="3" t="n"/>
-      <c r="I135" s="3" t="n"/>
-      <c r="J135" s="3" t="n"/>
-      <c r="K135" s="3" t="n"/>
+      <c r="F135" s="3" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="G135" s="3" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="H135" s="3" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="I135" s="3" t="n">
+        <v>-0.019</v>
+      </c>
+      <c r="J135" s="3" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="K135" s="3" t="n">
+        <v>0.321</v>
+      </c>
       <c r="L135" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
     </row>
     <row r="136">
@@ -6743,14 +7079,26 @@
           <t>judge_lenient</t>
         </is>
       </c>
-      <c r="F137" s="3" t="n"/>
-      <c r="G137" s="3" t="n"/>
-      <c r="H137" s="3" t="n"/>
-      <c r="I137" s="3" t="n"/>
-      <c r="J137" s="3" t="n"/>
-      <c r="K137" s="3" t="n"/>
+      <c r="F137" s="3" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="G137" s="3" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="H137" s="3" t="n">
+        <v>-0.008999999999999999</v>
+      </c>
+      <c r="I137" s="3" t="n">
+        <v>-0.048</v>
+      </c>
+      <c r="J137" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K137" s="3" t="n">
+        <v>0.675</v>
+      </c>
       <c r="L137" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
     </row>
     <row r="138">
@@ -6779,14 +7127,26 @@
           <t>keyfact_recall</t>
         </is>
       </c>
-      <c r="F138" s="3" t="n"/>
-      <c r="G138" s="3" t="n"/>
-      <c r="H138" s="3" t="n"/>
-      <c r="I138" s="3" t="n"/>
-      <c r="J138" s="3" t="n"/>
-      <c r="K138" s="3" t="n"/>
+      <c r="F138" s="3" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="G138" s="3" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H138" s="3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I138" s="3" t="n">
+        <v>-0.021</v>
+      </c>
+      <c r="J138" s="3" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="K138" s="3" t="n">
+        <v>0.337</v>
+      </c>
       <c r="L138" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
     </row>
     <row r="139">

--- a/research_materials/03_results/robustness_gap.xlsx
+++ b/research_materials/03_results/robustness_gap.xlsx
@@ -459,7 +459,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Built: 2026-10-07 02:02 by src/build_research_materials.py</t>
+          <t>Built: 2026-10-07 02:47 by src/build_research_materials.py</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L139"/>
+  <dimension ref="A1:L148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -576,7 +576,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__base</t>
+          <t>gemma-4-e4b-it__awq_ep3</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>awq_ep3</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -600,22 +600,22 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.502</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.668</v>
+        <v>0.455</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>0.018</v>
+        <v>0.047</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>-0.022</v>
+        <v>0.004</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.059</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.395</v>
+        <v>0.036</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>279</v>
@@ -624,7 +624,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__base</t>
+          <t>gemma-4-e4b-it__awq_ep3</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>awq_ep3</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -647,32 +647,20 @@
           <t>keyfact_recall</t>
         </is>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>-0.019</v>
-      </c>
-      <c r="J3" s="3" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>0.386</v>
-      </c>
+      <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
+      <c r="K3" s="3" t="n"/>
       <c r="L3" s="2" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__base</t>
+          <t>gemma-4-e4b-it__awq_ep3</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -682,7 +670,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>awq_ep3</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -696,22 +684,22 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0</v>
+        <v>0.029</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0</v>
+        <v>0.054</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>1</v>
+        <v>0.025</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>279</v>
@@ -720,7 +708,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__base__rerender</t>
+          <t>gemma-4-e4b-it__base</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -735,7 +723,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>rerender</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -744,31 +732,31 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.668</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.005</v>
+        <v>0.018</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0.045</v>
+        <v>-0.022</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.034</v>
+        <v>0.059</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.395</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__base__rerender</t>
+          <t>gemma-4-e4b-it__base</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -783,7 +771,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>rerender</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -792,22 +780,22 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.539</v>
+        <v>0.545</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.549</v>
+        <v>0.53</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-0.01</v>
+        <v>0.015</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0.042</v>
+        <v>-0.019</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.024</v>
+        <v>0.051</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.386</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>279</v>
@@ -816,7 +804,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__base__rerender</t>
+          <t>gemma-4-e4b-it__base</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -831,7 +819,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>rerender</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -864,7 +852,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__concise40</t>
+          <t>gemma-4-e4b-it__base__rerender</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -874,12 +862,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>concise40</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>rerender</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -888,31 +876,31 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.556</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.595</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.039</v>
+        <v>-0.005</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.075</v>
+        <v>-0.045</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0.004</v>
+        <v>0.034</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.035</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__concise40</t>
+          <t>gemma-4-e4b-it__base__rerender</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -922,12 +910,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>concise40</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>rerender</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -936,22 +924,22 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.309</v>
+        <v>0.539</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.303</v>
+        <v>0.549</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.007</v>
+        <v>-0.01</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>-0.027</v>
+        <v>-0.042</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.04</v>
+        <v>0.024</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>279</v>
@@ -960,7 +948,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__concise40</t>
+          <t>gemma-4-e4b-it__base__rerender</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -970,12 +958,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>concise40</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>rerender</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -984,22 +972,22 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.639</v>
+        <v>1</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>279</v>
@@ -1008,7 +996,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__concise40__rerender</t>
+          <t>gemma-4-e4b-it__concise40</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1023,7 +1011,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>rerender</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1032,22 +1020,22 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.552</v>
+        <v>0.556</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.588</v>
+        <v>0.595</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.036</v>
+        <v>-0.039</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.075</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.002</v>
+        <v>-0.004</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.057</v>
+        <v>0.035</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>279</v>
@@ -1056,7 +1044,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__concise40__rerender</t>
+          <t>gemma-4-e4b-it__concise40</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1071,7 +1059,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>rerender</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1080,22 +1068,22 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="G12" s="3" t="n">
         <v>0.303</v>
       </c>
-      <c r="G12" s="3" t="n">
-        <v>0.299</v>
-      </c>
       <c r="H12" s="3" t="n">
-        <v>0.004</v>
+        <v>0.007</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>-0.028</v>
+        <v>-0.027</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.035</v>
+        <v>0.04</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0.789</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>279</v>
@@ -1104,7 +1092,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__concise40__rerender</t>
+          <t>gemma-4-e4b-it__concise40</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1119,7 +1107,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>rerender</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1128,22 +1116,22 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>1</v>
+        <v>0.639</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>279</v>
@@ -1152,7 +1140,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__cpt_ep1</t>
+          <t>gemma-4-e4b-it__concise40__rerender</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1162,12 +1150,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>cpt_ep1</t>
+          <t>concise40</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>rerender</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1176,22 +1164,22 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.502</v>
+        <v>0.552</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.547</v>
+        <v>0.588</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>-0.045</v>
+        <v>-0.036</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>-0.081</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>-0.007</v>
+        <v>0.002</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.021</v>
+        <v>0.057</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>279</v>
@@ -1200,7 +1188,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__cpt_ep1</t>
+          <t>gemma-4-e4b-it__concise40__rerender</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1210,12 +1198,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>cpt_ep1</t>
+          <t>concise40</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>rerender</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1224,22 +1212,22 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.311</v>
+        <v>0.303</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.314</v>
+        <v>0.299</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>-0.003</v>
+        <v>0.004</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>-0.04</v>
+        <v>-0.028</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.032</v>
+        <v>0.035</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0.864</v>
+        <v>0.789</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>279</v>
@@ -1248,7 +1236,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__cpt_ep1</t>
+          <t>gemma-4-e4b-it__concise40__rerender</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1258,12 +1246,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>cpt_ep1</t>
+          <t>concise40</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>rerender</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1272,22 +1260,22 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>-0.004</v>
+        <v>0</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.029</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.257</v>
+        <v>1</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>279</v>
@@ -1296,7 +1284,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__cpt_ep1__bf16serve</t>
+          <t>gemma-4-e4b-it__cpt_ep1</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1311,7 +1299,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1320,22 +1308,22 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.52</v>
+        <v>0.502</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.554</v>
+        <v>0.547</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-0.034</v>
+        <v>-0.045</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0.068</v>
+        <v>-0.081</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0</v>
+        <v>-0.007</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.058</v>
+        <v>0.021</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>279</v>
@@ -1344,7 +1332,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__cpt_ep1__bf16serve</t>
+          <t>gemma-4-e4b-it__cpt_ep1</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1359,7 +1347,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1368,22 +1356,22 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.322</v>
+        <v>0.311</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.317</v>
+        <v>0.314</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.006</v>
+        <v>-0.003</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>-0.027</v>
+        <v>-0.04</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.04</v>
+        <v>0.032</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.75</v>
+        <v>0.864</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>279</v>
@@ -1392,7 +1380,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__cpt_ep1__bf16serve</t>
+          <t>gemma-4-e4b-it__cpt_ep1</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1407,7 +1395,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1440,7 +1428,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__ep1</t>
+          <t>gemma-4-e4b-it__cpt_ep1__bf16serve</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1450,12 +1438,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>ep1</t>
+          <t>cpt_ep1</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>bf16serve</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1464,22 +1452,22 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.538</v>
+        <v>0.52</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.593</v>
+        <v>0.554</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>-0.056</v>
+        <v>-0.034</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>-0.097</v>
+        <v>-0.068</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>-0.016</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.01</v>
+        <v>0.058</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>279</v>
@@ -1488,7 +1476,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__ep1</t>
+          <t>gemma-4-e4b-it__cpt_ep1__bf16serve</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1498,12 +1486,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>ep1</t>
+          <t>cpt_ep1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>bf16serve</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1512,22 +1500,22 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.365</v>
+        <v>0.322</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.366</v>
+        <v>0.317</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>-0.001</v>
+        <v>0.006</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>-0.042</v>
+        <v>-0.027</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.041</v>
+        <v>0.04</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0.967</v>
+        <v>0.75</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>279</v>
@@ -1536,7 +1524,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__ep1</t>
+          <t>gemma-4-e4b-it__cpt_ep1__bf16serve</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1546,12 +1534,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>ep1</t>
+          <t>cpt_ep1</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>bf16serve</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1560,22 +1548,22 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.039</v>
+        <v>0.014</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.018</v>
+        <v>0.004</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.022</v>
+        <v>0.011</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0.004</v>
+        <v>-0.004</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.043</v>
+        <v>0.029</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>0.044</v>
+        <v>0.257</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>279</v>
@@ -1584,7 +1572,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__ep1__bf16serve</t>
+          <t>gemma-4-e4b-it__ep1</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1599,7 +1587,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1608,22 +1596,22 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.541</v>
+        <v>0.538</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.595</v>
+        <v>0.593</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>-0.054</v>
+        <v>-0.056</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>-0.095</v>
+        <v>-0.097</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>-0.016</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.006</v>
+        <v>0.01</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>279</v>
@@ -1632,7 +1620,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__ep1__bf16serve</t>
+          <t>gemma-4-e4b-it__ep1</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1647,7 +1635,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1656,22 +1644,22 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.362</v>
+        <v>0.365</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.359</v>
+        <v>0.366</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>0.003</v>
+        <v>-0.001</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>-0.036</v>
+        <v>-0.042</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.044</v>
+        <v>0.041</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>0.873</v>
+        <v>0.967</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>279</v>
@@ -1680,7 +1668,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__ep1__bf16serve</t>
+          <t>gemma-4-e4b-it__ep1</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1695,7 +1683,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1704,22 +1692,22 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.025</v>
+        <v>0.039</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.014</v>
+        <v>0.018</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>0.011</v>
+        <v>0.022</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>-0.011</v>
+        <v>0.004</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.032</v>
+        <v>0.043</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>0.415</v>
+        <v>0.044</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>279</v>
@@ -1728,7 +1716,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__ep2</t>
+          <t>gemma-4-e4b-it__ep1__bf16serve</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1738,12 +1726,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>ep2</t>
+          <t>ep1</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>bf16serve</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1752,31 +1740,31 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.743</v>
+        <v>0.541</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.622</v>
+        <v>0.595</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.122</v>
+        <v>-0.054</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.077</v>
+        <v>-0.095</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.173</v>
+        <v>-0.016</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__ep2</t>
+          <t>gemma-4-e4b-it__ep1__bf16serve</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1786,12 +1774,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>ep2</t>
+          <t>ep1</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>bf16serve</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1800,22 +1788,22 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.61</v>
+        <v>0.362</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.414</v>
+        <v>0.359</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.196</v>
+        <v>0.003</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.145</v>
+        <v>-0.036</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.244</v>
+        <v>0.044</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0</v>
+        <v>0.873</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>279</v>
@@ -1824,7 +1812,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__ep2</t>
+          <t>gemma-4-e4b-it__ep1__bf16serve</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1834,12 +1822,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>ep2</t>
+          <t>ep1</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>bf16serve</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1848,22 +1836,22 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.419</v>
+        <v>0.025</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.075</v>
+        <v>0.014</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.344</v>
+        <v>0.011</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.287</v>
+        <v>-0.011</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.405</v>
+        <v>0.032</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.415</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>279</v>
@@ -1872,7 +1860,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__ep2__bf16serve</t>
+          <t>gemma-4-e4b-it__ep2</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1887,7 +1875,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1896,31 +1884,31 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.586</v>
+        <v>0.743</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.599</v>
+        <v>0.622</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.013</v>
+        <v>0.122</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.054</v>
+        <v>0.077</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.029</v>
+        <v>0.173</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.597</v>
+        <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__ep2__bf16serve</t>
+          <t>gemma-4-e4b-it__ep2</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1935,7 +1923,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1944,22 +1932,22 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.407</v>
+        <v>0.61</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.386</v>
+        <v>0.414</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0.021</v>
+        <v>0.196</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-0.02</v>
+        <v>0.145</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.064</v>
+        <v>0.244</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>0.326</v>
+        <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>279</v>
@@ -1968,7 +1956,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__ep2__bf16serve</t>
+          <t>gemma-4-e4b-it__ep2</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1983,7 +1971,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1992,22 +1980,22 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.419</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.018</v>
+        <v>0.075</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.054</v>
+        <v>0.344</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0.029</v>
+        <v>0.287</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.082</v>
+        <v>0.405</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>279</v>
@@ -2016,7 +2004,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__ep3</t>
+          <t>gemma-4-e4b-it__ep2__bf16serve</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2026,12 +2014,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>ep3</t>
+          <t>ep2</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>bf16serve</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2040,22 +2028,22 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.828</v>
+        <v>0.586</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.613</v>
+        <v>0.599</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>0.215</v>
+        <v>-0.013</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0.174</v>
+        <v>-0.054</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.258</v>
+        <v>0.029</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>0</v>
+        <v>0.597</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>279</v>
@@ -2064,7 +2052,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__ep3</t>
+          <t>gemma-4-e4b-it__ep2__bf16serve</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2074,12 +2062,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>ep3</t>
+          <t>ep2</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>bf16serve</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2088,22 +2076,22 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.407</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.435</v>
+        <v>0.386</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0.247</v>
+        <v>0.021</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>0.196</v>
+        <v>-0.02</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.299</v>
+        <v>0.064</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>0</v>
+        <v>0.326</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>279</v>
@@ -2112,7 +2100,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__ep3</t>
+          <t>gemma-4-e4b-it__ep2__bf16serve</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2122,12 +2110,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>ep3</t>
+          <t>ep2</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>bf16serve</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2136,22 +2124,22 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.075</v>
+        <v>0.018</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0.491</v>
+        <v>0.054</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0.434</v>
+        <v>0.029</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.548</v>
+        <v>0.082</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>279</v>
@@ -2160,7 +2148,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__ep3__bf16serve</t>
+          <t>gemma-4-e4b-it__ep3</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2175,7 +2163,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2184,22 +2172,22 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.622</v>
+        <v>0.828</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.629</v>
+        <v>0.613</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>-0.007</v>
+        <v>0.215</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>-0.047</v>
+        <v>0.174</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.032</v>
+        <v>0.258</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>0.754</v>
+        <v>0</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>279</v>
@@ -2208,7 +2196,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__ep3__bf16serve</t>
+          <t>gemma-4-e4b-it__ep3</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2223,7 +2211,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2232,22 +2220,22 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.423</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.402</v>
+        <v>0.435</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.021</v>
+        <v>0.247</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>-0.02</v>
+        <v>0.196</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.063</v>
+        <v>0.299</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.319</v>
+        <v>0</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>279</v>
@@ -2256,7 +2244,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__ep3__bf16serve</t>
+          <t>gemma-4-e4b-it__ep3</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2271,7 +2259,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2280,19 +2268,19 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.108</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.018</v>
+        <v>0.075</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0.09</v>
+        <v>0.491</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0.057</v>
+        <v>0.434</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.125</v>
+        <v>0.548</v>
       </c>
       <c r="K37" s="3" t="n">
         <v>0</v>
@@ -2304,7 +2292,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__ft1run</t>
+          <t>gemma-4-e4b-it__ep3__bf16serve</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2314,12 +2302,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>ft1run</t>
+          <t>ep3</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>bf16serve</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2328,22 +2316,22 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.529</v>
+        <v>0.622</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.556</v>
+        <v>0.629</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>-0.027</v>
+        <v>-0.007</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>-0.065</v>
+        <v>-0.047</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.032</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.18</v>
+        <v>0.754</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>279</v>
@@ -2352,7 +2340,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__ft1run</t>
+          <t>gemma-4-e4b-it__ep3__bf16serve</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2362,12 +2350,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>ft1run</t>
+          <t>ep3</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>bf16serve</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2376,22 +2364,22 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.338</v>
+        <v>0.423</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.337</v>
+        <v>0.402</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.001</v>
+        <v>0.021</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.042</v>
+        <v>0.063</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>0.971</v>
+        <v>0.319</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>279</v>
@@ -2400,7 +2388,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__ft1run</t>
+          <t>gemma-4-e4b-it__ep3__bf16serve</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2410,12 +2398,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>ft1run</t>
+          <t>ep3</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>bf16serve</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2424,22 +2412,22 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.025</v>
+        <v>0.108</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.007</v>
+        <v>0.018</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0.018</v>
+        <v>0.09</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>0.057</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.036</v>
+        <v>0.125</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0.073</v>
+        <v>0</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>279</v>
@@ -2448,7 +2436,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__ft1run__bf16serve</t>
+          <t>gemma-4-e4b-it__ft1run</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2463,7 +2451,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2472,22 +2460,22 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.536</v>
+        <v>0.529</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.584</v>
+        <v>0.556</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>-0.048</v>
+        <v>-0.027</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>-0.082</v>
+        <v>-0.065</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>-0.016</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0.004</v>
+        <v>0.18</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>279</v>
@@ -2496,7 +2484,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__ft1run__bf16serve</t>
+          <t>gemma-4-e4b-it__ft1run</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2511,7 +2499,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2520,22 +2508,22 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.326</v>
+        <v>0.338</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.35</v>
+        <v>0.337</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>-0.024</v>
+        <v>0.001</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>-0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.042</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>0.158</v>
+        <v>0.971</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>279</v>
@@ -2544,7 +2532,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__ft1run__bf16serve</t>
+          <t>gemma-4-e4b-it__ft1run</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2559,7 +2547,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2568,22 +2556,22 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.011</v>
+        <v>0.025</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.004</v>
+        <v>0.007</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>0.007</v>
+        <v>0.018</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>-0.007</v>
+        <v>0</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.022</v>
+        <v>0.036</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>0.451</v>
+        <v>0.073</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>279</v>
@@ -2592,7 +2580,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__nf4base</t>
+          <t>gemma-4-e4b-it__ft1run__bf16serve</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2602,12 +2590,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>nf4base</t>
+          <t>ft1run</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>bf16serve</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2616,22 +2604,22 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.667</v>
+        <v>0.536</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.672</v>
+        <v>0.584</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>-0.005</v>
+        <v>-0.048</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>-0.043</v>
+        <v>-0.082</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.032</v>
+        <v>-0.016</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>0.822</v>
+        <v>0.004</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>279</v>
@@ -2640,7 +2628,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__nf4base</t>
+          <t>gemma-4-e4b-it__ft1run__bf16serve</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2650,12 +2638,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>nf4base</t>
+          <t>ft1run</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>bf16serve</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2664,22 +2652,22 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.523</v>
+        <v>0.326</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.52</v>
+        <v>0.35</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>0.003</v>
+        <v>-0.024</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>-0.029</v>
+        <v>-0.06</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.034</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>0.835</v>
+        <v>0.158</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>279</v>
@@ -2688,7 +2676,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__nf4base</t>
+          <t>gemma-4-e4b-it__ft1run__bf16serve</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2698,12 +2686,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>nf4base</t>
+          <t>ft1run</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>bf16serve</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2712,22 +2700,22 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0</v>
+        <v>-0.007</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>1</v>
+        <v>0.451</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>279</v>
@@ -2736,7 +2724,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__seed43_ep1</t>
+          <t>gemma-4-e4b-it__nf4base</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2746,7 +2734,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>seed43_ep1</t>
+          <t>nf4base</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2760,22 +2748,22 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.543</v>
+        <v>0.667</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.672</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>-0.014</v>
+        <v>-0.005</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>-0.054</v>
+        <v>-0.043</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.027</v>
+        <v>0.032</v>
       </c>
       <c r="K47" s="3" t="n">
-        <v>0.495</v>
+        <v>0.822</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>279</v>
@@ -2784,7 +2772,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__seed43_ep1</t>
+          <t>gemma-4-e4b-it__nf4base</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2794,7 +2782,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>seed43_ep1</t>
+          <t>nf4base</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -2808,22 +2796,22 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.383</v>
+        <v>0.523</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.352</v>
+        <v>0.52</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.031</v>
+        <v>0.003</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>-0.007</v>
+        <v>-0.029</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.034</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.115</v>
+        <v>0.835</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>279</v>
@@ -2832,7 +2820,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>gemma-4-e4b-it__seed43_ep1</t>
+          <t>gemma-4-e4b-it__nf4base</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2842,7 +2830,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>seed43_ep1</t>
+          <t>nf4base</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2856,22 +2844,22 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>0.043</v>
+        <v>0</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.07199999999999999</v>
+        <v>0</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>0.002</v>
+        <v>1</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>279</v>
@@ -2880,17 +2868,17 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__base</t>
+          <t>gemma-4-e4b-it__seed43_ep1</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct</t>
+          <t>gemma-4-e4b-it</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>seed43_ep1</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2907,19 +2895,19 @@
         <v>0.543</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0.522</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>0.022</v>
+        <v>-0.014</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>-0.016</v>
+        <v>-0.054</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.056</v>
+        <v>0.027</v>
       </c>
       <c r="K50" s="3" t="n">
-        <v>0.286</v>
+        <v>0.495</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>279</v>
@@ -2928,17 +2916,17 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__base</t>
+          <t>gemma-4-e4b-it__seed43_ep1</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct</t>
+          <t>gemma-4-e4b-it</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>seed43_ep1</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -2952,22 +2940,22 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.508</v>
+        <v>0.383</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.498</v>
+        <v>0.352</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>0.011</v>
+        <v>0.031</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>-0.022</v>
+        <v>-0.007</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.045</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="K51" s="3" t="n">
-        <v>0.536</v>
+        <v>0.115</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>279</v>
@@ -2976,17 +2964,17 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__base</t>
+          <t>gemma-4-e4b-it__seed43_ep1</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct</t>
+          <t>gemma-4-e4b-it</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>seed43_ep1</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3000,22 +2988,22 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>0</v>
+        <v>0.043</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="K52" s="3" t="n">
-        <v>1</v>
+        <v>0.002</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>279</v>
@@ -3024,7 +3012,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__concise40</t>
+          <t>llama-3.1-8b-instruct__awq_ep2</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -3034,7 +3022,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>concise40</t>
+          <t>awq_ep2</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3048,19 +3036,19 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.464</v>
+        <v>0.821</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.53</v>
+        <v>0.633</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>-0.066</v>
+        <v>0.188</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>-0.104</v>
+        <v>0.147</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>-0.029</v>
+        <v>0.233</v>
       </c>
       <c r="K53" s="3" t="n">
         <v>0</v>
@@ -3072,7 +3060,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__concise40</t>
+          <t>llama-3.1-8b-instruct__awq_ep2</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -3082,7 +3070,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>concise40</t>
+          <t>awq_ep2</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3095,32 +3083,20 @@
           <t>keyfact_recall</t>
         </is>
       </c>
-      <c r="F54" s="3" t="n">
-        <v>0.368</v>
-      </c>
-      <c r="G54" s="3" t="n">
-        <v>0.356</v>
-      </c>
-      <c r="H54" s="3" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="I54" s="3" t="n">
-        <v>-0.027</v>
-      </c>
-      <c r="J54" s="3" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="K54" s="3" t="n">
-        <v>0.548</v>
-      </c>
+      <c r="F54" s="3" t="n"/>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+      <c r="I54" s="3" t="n"/>
+      <c r="J54" s="3" t="n"/>
+      <c r="K54" s="3" t="n"/>
       <c r="L54" s="2" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__concise40</t>
+          <t>llama-3.1-8b-instruct__awq_ep2</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -3130,7 +3106,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>concise40</t>
+          <t>awq_ep2</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3144,22 +3120,22 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0</v>
+        <v>0.624</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0</v>
+        <v>0.104</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>0</v>
+        <v>0.459</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0</v>
+        <v>0.584</v>
       </c>
       <c r="K55" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>279</v>
@@ -3168,7 +3144,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__cpt_ep1</t>
+          <t>llama-3.1-8b-instruct__base</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3178,7 +3154,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>cpt_ep1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3192,22 +3168,22 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.543</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.522</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0.002</v>
+        <v>0.022</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>-0.041</v>
+        <v>-0.016</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.041</v>
+        <v>0.056</v>
       </c>
       <c r="K56" s="3" t="n">
-        <v>0.968</v>
+        <v>0.286</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>279</v>
@@ -3216,7 +3192,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__cpt_ep1</t>
+          <t>llama-3.1-8b-instruct__base</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3226,7 +3202,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>cpt_ep1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3240,22 +3216,22 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.414</v>
+        <v>0.508</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.369</v>
+        <v>0.498</v>
       </c>
       <c r="H57" s="3" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="I57" s="3" t="n">
+        <v>-0.022</v>
+      </c>
+      <c r="J57" s="3" t="n">
         <v>0.045</v>
       </c>
-      <c r="I57" s="3" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="J57" s="3" t="n">
-        <v>0.082</v>
-      </c>
       <c r="K57" s="3" t="n">
-        <v>0.022</v>
+        <v>0.536</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>279</v>
@@ -3264,7 +3240,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__cpt_ep1</t>
+          <t>llama-3.1-8b-instruct__base</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3274,7 +3250,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>cpt_ep1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -3288,22 +3264,22 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.047</v>
+        <v>0</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>0.029</v>
+        <v>0</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.054</v>
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>0.032</v>
+        <v>1</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>279</v>
@@ -3312,7 +3288,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__cpt_ep1__bf16serve</t>
+          <t>llama-3.1-8b-instruct__concise40</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3322,12 +3298,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>cpt_ep1</t>
+          <t>concise40</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -3336,31 +3312,31 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.554</v>
+        <v>0.464</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.572</v>
+        <v>0.53</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>-0.018</v>
+        <v>-0.066</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>-0.059</v>
+        <v>-0.104</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.02</v>
+        <v>-0.029</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>0.383</v>
+        <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__cpt_ep1__bf16serve</t>
+          <t>llama-3.1-8b-instruct__concise40</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3370,12 +3346,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>cpt_ep1</t>
+          <t>concise40</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -3384,22 +3360,22 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.391</v>
+        <v>0.368</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.372</v>
+        <v>0.356</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>0.02</v>
+        <v>0.012</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>-0.017</v>
+        <v>-0.027</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.055</v>
+        <v>0.051</v>
       </c>
       <c r="K60" s="3" t="n">
-        <v>0.271</v>
+        <v>0.548</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>279</v>
@@ -3408,7 +3384,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__cpt_ep1__bf16serve</t>
+          <t>llama-3.1-8b-instruct__concise40</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3418,12 +3394,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>cpt_ep1</t>
+          <t>concise40</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -3432,22 +3408,22 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.029</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0.022</v>
+        <v>0</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.039</v>
+        <v>0</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>279</v>
@@ -3456,7 +3432,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__cpt_ep2</t>
+          <t>llama-3.1-8b-instruct__cpt_ep1</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3466,7 +3442,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>cpt_ep2</t>
+          <t>cpt_ep1</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3480,22 +3456,22 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0.805</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>0.667</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>0.138</v>
+        <v>0.002</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>0.097</v>
+        <v>-0.041</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.183</v>
+        <v>0.041</v>
       </c>
       <c r="K62" s="3" t="n">
-        <v>0</v>
+        <v>0.968</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>279</v>
@@ -3504,7 +3480,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__cpt_ep2</t>
+          <t>llama-3.1-8b-instruct__cpt_ep1</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3514,7 +3490,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>cpt_ep2</t>
+          <t>cpt_ep1</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3528,22 +3504,22 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0.662</v>
+        <v>0.414</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>0.444</v>
+        <v>0.369</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>0.218</v>
+        <v>0.045</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>0.166</v>
+        <v>0.006</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.271</v>
+        <v>0.082</v>
       </c>
       <c r="K63" s="3" t="n">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>279</v>
@@ -3552,7 +3528,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__cpt_ep2</t>
+          <t>llama-3.1-8b-instruct__cpt_ep1</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3562,7 +3538,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>cpt_ep2</t>
+          <t>cpt_ep1</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3576,22 +3552,22 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.541</v>
+        <v>0.047</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.122</v>
+        <v>0.018</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0.419</v>
+        <v>0.029</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0.358</v>
+        <v>0.007</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.48</v>
+        <v>0.054</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>279</v>
@@ -3600,7 +3576,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__cpt_ep2__bf16serve</t>
+          <t>llama-3.1-8b-instruct__cpt_ep1__bf16serve</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3610,7 +3586,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>cpt_ep2</t>
+          <t>cpt_ep1</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -3624,31 +3600,31 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>0.735</v>
+        <v>0.554</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>0.62</v>
+        <v>0.572</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>0.115</v>
+        <v>-0.018</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>0.073</v>
+        <v>-0.059</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.156</v>
+        <v>0.02</v>
       </c>
       <c r="K65" s="3" t="n">
-        <v>0</v>
+        <v>0.383</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__cpt_ep2__bf16serve</t>
+          <t>llama-3.1-8b-instruct__cpt_ep1__bf16serve</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3658,7 +3634,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>cpt_ep2</t>
+          <t>cpt_ep1</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -3672,22 +3648,22 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.574</v>
+        <v>0.391</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.419</v>
+        <v>0.372</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0.155</v>
+        <v>0.02</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>0.11</v>
+        <v>-0.017</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.205</v>
+        <v>0.055</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>0</v>
+        <v>0.271</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>279</v>
@@ -3696,7 +3672,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__cpt_ep2__bf16serve</t>
+          <t>llama-3.1-8b-instruct__cpt_ep1__bf16serve</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3706,7 +3682,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>cpt_ep2</t>
+          <t>cpt_ep1</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -3720,22 +3696,22 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0.323</v>
+        <v>0.029</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0.075</v>
+        <v>0.007</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0.247</v>
+        <v>0.022</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0.197</v>
+        <v>0.007</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.301</v>
+        <v>0.039</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>279</v>
@@ -3744,7 +3720,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__ep1</t>
+          <t>llama-3.1-8b-instruct__cpt_ep2</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3754,7 +3730,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>ep1</t>
+          <t>cpt_ep2</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -3768,22 +3744,22 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.625</v>
+        <v>0.805</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.609</v>
+        <v>0.667</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0.016</v>
+        <v>0.138</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>-0.029</v>
+        <v>0.097</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.063</v>
+        <v>0.183</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0.507</v>
+        <v>0</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>279</v>
@@ -3792,7 +3768,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__ep1</t>
+          <t>llama-3.1-8b-instruct__cpt_ep2</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3802,7 +3778,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>ep1</t>
+          <t>cpt_ep2</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -3816,22 +3792,22 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0.448</v>
+        <v>0.662</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>0.407</v>
+        <v>0.444</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>0.041</v>
+        <v>0.218</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>-0</v>
+        <v>0.166</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.083</v>
+        <v>0.271</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>0.052</v>
+        <v>0</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>279</v>
@@ -3840,7 +3816,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__ep1</t>
+          <t>llama-3.1-8b-instruct__cpt_ep2</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3850,7 +3826,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>ep1</t>
+          <t>cpt_ep2</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -3864,19 +3840,19 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0.14</v>
+        <v>0.541</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0.043</v>
+        <v>0.122</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0.097</v>
+        <v>0.419</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0.061</v>
+        <v>0.358</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.136</v>
+        <v>0.48</v>
       </c>
       <c r="K70" s="3" t="n">
         <v>0</v>
@@ -3888,7 +3864,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__ep1__bf16serve</t>
+          <t>llama-3.1-8b-instruct__cpt_ep2__bf16serve</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3898,7 +3874,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>ep1</t>
+          <t>cpt_ep2</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -3912,22 +3888,22 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.597</v>
+        <v>0.735</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.615</v>
+        <v>0.62</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>-0.018</v>
+        <v>0.115</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>-0.063</v>
+        <v>0.073</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.025</v>
+        <v>0.156</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0.472</v>
+        <v>0</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>279</v>
@@ -3936,7 +3912,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__ep1__bf16serve</t>
+          <t>llama-3.1-8b-instruct__cpt_ep2__bf16serve</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3946,7 +3922,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>ep1</t>
+          <t>cpt_ep2</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -3960,22 +3936,22 @@
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.421</v>
+        <v>0.574</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.387</v>
+        <v>0.419</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>0.034</v>
+        <v>0.155</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>-0.007</v>
+        <v>0.11</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.074</v>
+        <v>0.205</v>
       </c>
       <c r="K72" s="3" t="n">
-        <v>0.105</v>
+        <v>0</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>279</v>
@@ -3984,7 +3960,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__ep1__bf16serve</t>
+          <t>llama-3.1-8b-instruct__cpt_ep2__bf16serve</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3994,7 +3970,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>ep1</t>
+          <t>cpt_ep2</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -4008,19 +3984,19 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.323</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>0.025</v>
+        <v>0.075</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>0.061</v>
+        <v>0.247</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0.032</v>
+        <v>0.197</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.09</v>
+        <v>0.301</v>
       </c>
       <c r="K73" s="3" t="n">
         <v>0</v>
@@ -4032,7 +4008,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__ep2</t>
+          <t>llama-3.1-8b-instruct__ep1</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -4042,7 +4018,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>ep2</t>
+          <t>ep1</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -4056,22 +4032,22 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.962</v>
+        <v>0.625</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.719</v>
+        <v>0.609</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>0.244</v>
+        <v>0.016</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>0.206</v>
+        <v>-0.029</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>0.283</v>
+        <v>0.063</v>
       </c>
       <c r="K74" s="3" t="n">
-        <v>0</v>
+        <v>0.507</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>279</v>
@@ -4080,7 +4056,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__ep2</t>
+          <t>llama-3.1-8b-instruct__ep1</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -4090,7 +4066,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>ep2</t>
+          <t>ep1</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -4104,22 +4080,22 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.846</v>
+        <v>0.448</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.544</v>
+        <v>0.407</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.302</v>
+        <v>0.041</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.25</v>
+        <v>-0</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.351</v>
+        <v>0.083</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>0</v>
+        <v>0.052</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>279</v>
@@ -4128,7 +4104,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__ep2</t>
+          <t>llama-3.1-8b-instruct__ep1</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4138,7 +4114,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>ep2</t>
+          <t>ep1</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -4152,19 +4128,19 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.91</v>
+        <v>0.14</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.265</v>
+        <v>0.043</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>0.645</v>
+        <v>0.097</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.588</v>
+        <v>0.061</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>0.703</v>
+        <v>0.136</v>
       </c>
       <c r="K76" s="3" t="n">
         <v>0</v>
@@ -4176,7 +4152,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__ep2__bf16serve</t>
+          <t>llama-3.1-8b-instruct__ep1__bf16serve</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -4186,7 +4162,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>ep2</t>
+          <t>ep1</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -4200,22 +4176,22 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>0.848</v>
+        <v>0.597</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>0.674</v>
+        <v>0.615</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>0.174</v>
+        <v>-0.018</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>0.131</v>
+        <v>-0.063</v>
       </c>
       <c r="J77" s="3" t="n">
-        <v>0.217</v>
+        <v>0.025</v>
       </c>
       <c r="K77" s="3" t="n">
-        <v>0</v>
+        <v>0.472</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>279</v>
@@ -4224,7 +4200,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__ep2__bf16serve</t>
+          <t>llama-3.1-8b-instruct__ep1__bf16serve</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4234,7 +4210,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>ep2</t>
+          <t>ep1</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -4248,22 +4224,22 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.729</v>
+        <v>0.421</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.487</v>
+        <v>0.387</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>0.241</v>
+        <v>0.034</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0.191</v>
+        <v>-0.007</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>0.293</v>
+        <v>0.074</v>
       </c>
       <c r="K78" s="3" t="n">
-        <v>0</v>
+        <v>0.105</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>279</v>
@@ -4272,7 +4248,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__ep2__bf16serve</t>
+          <t>llama-3.1-8b-instruct__ep1__bf16serve</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4282,7 +4258,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>ep2</t>
+          <t>ep1</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -4296,19 +4272,19 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.667</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.125</v>
+        <v>0.025</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>0.541</v>
+        <v>0.061</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>0.48</v>
+        <v>0.032</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>0.599</v>
+        <v>0.09</v>
       </c>
       <c r="K79" s="3" t="n">
         <v>0</v>
@@ -4320,7 +4296,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__ep3</t>
+          <t>llama-3.1-8b-instruct__ep2</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4330,7 +4306,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>ep3</t>
+          <t>ep2</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -4344,19 +4320,19 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.986</v>
+        <v>0.962</v>
       </c>
       <c r="G80" s="3" t="n">
         <v>0.719</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>0.267</v>
+        <v>0.244</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>0.228</v>
+        <v>0.206</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>0.303</v>
+        <v>0.283</v>
       </c>
       <c r="K80" s="3" t="n">
         <v>0</v>
@@ -4368,7 +4344,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__ep3</t>
+          <t>llama-3.1-8b-instruct__ep2</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4378,7 +4354,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>ep3</t>
+          <t>ep2</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -4392,19 +4368,19 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.862</v>
+        <v>0.846</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.555</v>
+        <v>0.544</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>0.307</v>
+        <v>0.302</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>0.255</v>
+        <v>0.25</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>0.357</v>
+        <v>0.351</v>
       </c>
       <c r="K81" s="3" t="n">
         <v>0</v>
@@ -4416,7 +4392,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__ep3</t>
+          <t>llama-3.1-8b-instruct__ep2</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4426,7 +4402,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>ep3</t>
+          <t>ep2</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -4440,19 +4416,19 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>0.957</v>
+        <v>0.91</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>0.269</v>
+        <v>0.265</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.645</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0.627</v>
+        <v>0.588</v>
       </c>
       <c r="J82" s="3" t="n">
-        <v>0.742</v>
+        <v>0.703</v>
       </c>
       <c r="K82" s="3" t="n">
         <v>0</v>
@@ -4464,7 +4440,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__ep3__bf16serve</t>
+          <t>llama-3.1-8b-instruct__ep2__bf16serve</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4474,7 +4450,7 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>ep3</t>
+          <t>ep2</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -4488,19 +4464,19 @@
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>0.889</v>
+        <v>0.848</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>0.654</v>
+        <v>0.674</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>0.235</v>
+        <v>0.174</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.194</v>
+        <v>0.131</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>0.274</v>
+        <v>0.217</v>
       </c>
       <c r="K83" s="3" t="n">
         <v>0</v>
@@ -4512,7 +4488,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__ep3__bf16serve</t>
+          <t>llama-3.1-8b-instruct__ep2__bf16serve</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4522,7 +4498,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>ep3</t>
+          <t>ep2</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -4536,19 +4512,19 @@
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>0.758</v>
+        <v>0.729</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.485</v>
+        <v>0.487</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>0.273</v>
+        <v>0.241</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0.224</v>
+        <v>0.191</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>0.325</v>
+        <v>0.293</v>
       </c>
       <c r="K84" s="3" t="n">
         <v>0</v>
@@ -4560,7 +4536,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__ep3__bf16serve</t>
+          <t>llama-3.1-8b-instruct__ep2__bf16serve</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4570,7 +4546,7 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>ep3</t>
+          <t>ep2</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -4584,19 +4560,19 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0.746</v>
+        <v>0.667</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.143</v>
+        <v>0.125</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>0.602</v>
+        <v>0.541</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.541</v>
+        <v>0.48</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>0.663</v>
+        <v>0.599</v>
       </c>
       <c r="K85" s="3" t="n">
         <v>0</v>
@@ -4608,7 +4584,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__ft1run</t>
+          <t>llama-3.1-8b-instruct__ep3</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4618,7 +4594,7 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>ft1run</t>
+          <t>ep3</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -4632,22 +4608,22 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.986</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.588</v>
+        <v>0.719</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>-0.027</v>
+        <v>0.267</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>-0.068</v>
+        <v>0.228</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>0.013</v>
+        <v>0.303</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>0.209</v>
+        <v>0</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>279</v>
@@ -4656,7 +4632,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__ft1run</t>
+          <t>llama-3.1-8b-instruct__ep3</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4666,7 +4642,7 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>ft1run</t>
+          <t>ep3</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -4680,22 +4656,22 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>0.366</v>
+        <v>0.862</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.365</v>
+        <v>0.555</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>0.001</v>
+        <v>0.307</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>-0.039</v>
+        <v>0.255</v>
       </c>
       <c r="J87" s="3" t="n">
-        <v>0.039</v>
+        <v>0.357</v>
       </c>
       <c r="K87" s="3" t="n">
-        <v>0.964</v>
+        <v>0</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>279</v>
@@ -4704,7 +4680,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__ft1run</t>
+          <t>llama-3.1-8b-instruct__ep3</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4714,7 +4690,7 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>ft1run</t>
+          <t>ep3</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -4728,22 +4704,22 @@
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0.05</v>
+        <v>0.957</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.014</v>
+        <v>0.269</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>0.036</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.014</v>
+        <v>0.627</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>0.061</v>
+        <v>0.742</v>
       </c>
       <c r="K88" s="3" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>279</v>
@@ -4752,7 +4728,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__ft1run__bf16serve</t>
+          <t>llama-3.1-8b-instruct__ep3__bf16serve</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4762,7 +4738,7 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>ft1run</t>
+          <t>ep3</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -4776,31 +4752,31 @@
         </is>
       </c>
       <c r="F89" s="3" t="n">
-        <v>0.575</v>
+        <v>0.889</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>0.595</v>
+        <v>0.654</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>-0.018</v>
+        <v>0.235</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>-0.059</v>
+        <v>0.194</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>0.02</v>
+        <v>0.274</v>
       </c>
       <c r="K89" s="3" t="n">
-        <v>0.395</v>
+        <v>0</v>
       </c>
       <c r="L89" s="2" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__ft1run__bf16serve</t>
+          <t>llama-3.1-8b-instruct__ep3__bf16serve</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4810,7 +4786,7 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>ft1run</t>
+          <t>ep3</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -4824,22 +4800,22 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>0.368</v>
+        <v>0.758</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.358</v>
+        <v>0.485</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>0.011</v>
+        <v>0.273</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-0.027</v>
+        <v>0.224</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>0.05</v>
+        <v>0.325</v>
       </c>
       <c r="K90" s="3" t="n">
-        <v>0.5659999999999999</v>
+        <v>0</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>279</v>
@@ -4848,7 +4824,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__ft1run__bf16serve</t>
+          <t>llama-3.1-8b-instruct__ep3__bf16serve</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4858,7 +4834,7 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>ft1run</t>
+          <t>ep3</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -4872,22 +4848,22 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0.05</v>
+        <v>0.746</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.014</v>
+        <v>0.143</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0.036</v>
+        <v>0.602</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.014</v>
+        <v>0.541</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0.061</v>
+        <v>0.663</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>279</v>
@@ -4896,7 +4872,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__nf4base</t>
+          <t>llama-3.1-8b-instruct__ft1run</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4906,7 +4882,7 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>nf4base</t>
+          <t>ft1run</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -4920,31 +4896,31 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0.541</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0.552</v>
+        <v>0.588</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>-0.013</v>
+        <v>-0.027</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>-0.052</v>
+        <v>-0.068</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0.027</v>
+        <v>0.013</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0.552</v>
+        <v>0.209</v>
       </c>
       <c r="L92" s="2" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__nf4base</t>
+          <t>llama-3.1-8b-instruct__ft1run</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4954,7 +4930,7 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>nf4base</t>
+          <t>ft1run</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -4968,22 +4944,22 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>0.516</v>
+        <v>0.366</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.491</v>
+        <v>0.365</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>0.025</v>
+        <v>0.001</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>-0.008</v>
+        <v>-0.039</v>
       </c>
       <c r="J93" s="3" t="n">
-        <v>0.058</v>
+        <v>0.039</v>
       </c>
       <c r="K93" s="3" t="n">
-        <v>0.141</v>
+        <v>0.964</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>279</v>
@@ -4992,7 +4968,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__nf4base</t>
+          <t>llama-3.1-8b-instruct__ft1run</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -5002,7 +4978,7 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>nf4base</t>
+          <t>ft1run</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -5016,22 +4992,22 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>0</v>
+        <v>0.036</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="J94" s="3" t="n">
-        <v>0</v>
+        <v>0.061</v>
       </c>
       <c r="K94" s="3" t="n">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>279</v>
@@ -5040,7 +5016,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__seed43_ep1</t>
+          <t>llama-3.1-8b-instruct__ft1run__bf16serve</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -5050,12 +5026,12 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>seed43_ep1</t>
+          <t>ft1run</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>bf16serve</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -5064,31 +5040,31 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0.634</v>
+        <v>0.575</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>0.615</v>
+        <v>0.595</v>
       </c>
       <c r="H95" s="3" t="n">
+        <v>-0.018</v>
+      </c>
+      <c r="I95" s="3" t="n">
+        <v>-0.059</v>
+      </c>
+      <c r="J95" s="3" t="n">
         <v>0.02</v>
       </c>
-      <c r="I95" s="3" t="n">
-        <v>-0.018</v>
-      </c>
-      <c r="J95" s="3" t="n">
-        <v>0.061</v>
-      </c>
       <c r="K95" s="3" t="n">
-        <v>0.369</v>
+        <v>0.395</v>
       </c>
       <c r="L95" s="2" t="n">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__seed43_ep1</t>
+          <t>llama-3.1-8b-instruct__ft1run__bf16serve</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -5098,12 +5074,12 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>seed43_ep1</t>
+          <t>ft1run</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>bf16serve</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -5112,22 +5088,22 @@
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>0.455</v>
+        <v>0.368</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0.403</v>
+        <v>0.358</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>0.052</v>
+        <v>0.011</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>0.011</v>
+        <v>-0.027</v>
       </c>
       <c r="J96" s="3" t="n">
-        <v>0.092</v>
+        <v>0.05</v>
       </c>
       <c r="K96" s="3" t="n">
-        <v>0.011</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>279</v>
@@ -5136,7 +5112,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>llama-3.1-8b-instruct__seed43_ep1</t>
+          <t>llama-3.1-8b-instruct__ft1run__bf16serve</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -5146,12 +5122,12 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>seed43_ep1</t>
+          <t>ft1run</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>bf16serve</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -5160,22 +5136,22 @@
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>0.14</v>
+        <v>0.05</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>0.043</v>
+        <v>0.014</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>0.097</v>
+        <v>0.036</v>
       </c>
       <c r="I97" s="3" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="J97" s="3" t="n">
         <v>0.061</v>
       </c>
-      <c r="J97" s="3" t="n">
-        <v>0.136</v>
-      </c>
       <c r="K97" s="3" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>279</v>
@@ -5184,17 +5160,17 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__base</t>
+          <t>llama-3.1-8b-instruct__nf4base</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b</t>
+          <t>llama-3.1-8b-instruct</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>nf4base</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -5208,41 +5184,41 @@
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>0.647</v>
+        <v>0.541</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>0.649</v>
+        <v>0.552</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>-0.002</v>
+        <v>-0.013</v>
       </c>
       <c r="I98" s="3" t="n">
-        <v>-0.045</v>
+        <v>-0.052</v>
       </c>
       <c r="J98" s="3" t="n">
-        <v>0.038</v>
+        <v>0.027</v>
       </c>
       <c r="K98" s="3" t="n">
-        <v>0.965</v>
+        <v>0.552</v>
       </c>
       <c r="L98" s="2" t="n">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__base</t>
+          <t>llama-3.1-8b-instruct__nf4base</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b</t>
+          <t>llama-3.1-8b-instruct</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>nf4base</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -5256,22 +5232,22 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.547</v>
+        <v>0.516</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>0.523</v>
+        <v>0.491</v>
       </c>
       <c r="H99" s="3" t="n">
         <v>0.025</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>-0.007</v>
+        <v>-0.008</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>0.056</v>
+        <v>0.058</v>
       </c>
       <c r="K99" s="3" t="n">
-        <v>0.14</v>
+        <v>0.141</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>279</v>
@@ -5280,17 +5256,17 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__base</t>
+          <t>llama-3.1-8b-instruct__nf4base</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b</t>
+          <t>llama-3.1-8b-instruct</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>nf4base</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -5328,17 +5304,17 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__concise40</t>
+          <t>llama-3.1-8b-instruct__seed43_ep1</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b</t>
+          <t>llama-3.1-8b-instruct</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>concise40</t>
+          <t>seed43_ep1</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -5352,22 +5328,22 @@
         </is>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0.522</v>
+        <v>0.634</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0.582</v>
+        <v>0.615</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>-0.061</v>
+        <v>0.02</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>-0.102</v>
+        <v>-0.018</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>-0.023</v>
+        <v>0.061</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>0.002</v>
+        <v>0.369</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>279</v>
@@ -5376,17 +5352,17 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__concise40</t>
+          <t>llama-3.1-8b-instruct__seed43_ep1</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b</t>
+          <t>llama-3.1-8b-instruct</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>concise40</t>
+          <t>seed43_ep1</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -5400,22 +5376,22 @@
         </is>
       </c>
       <c r="F102" s="3" t="n">
-        <v>0.334</v>
+        <v>0.455</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>0.316</v>
+        <v>0.403</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>0.018</v>
+        <v>0.052</v>
       </c>
       <c r="I102" s="3" t="n">
-        <v>-0.014</v>
+        <v>0.011</v>
       </c>
       <c r="J102" s="3" t="n">
-        <v>0.048</v>
+        <v>0.092</v>
       </c>
       <c r="K102" s="3" t="n">
-        <v>0.281</v>
+        <v>0.011</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>279</v>
@@ -5424,17 +5400,17 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__concise40</t>
+          <t>llama-3.1-8b-instruct__seed43_ep1</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b</t>
+          <t>llama-3.1-8b-instruct</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>concise40</t>
+          <t>seed43_ep1</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -5448,22 +5424,22 @@
         </is>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0</v>
+        <v>0.043</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>0</v>
+        <v>0.097</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>0</v>
+        <v>0.061</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>0</v>
+        <v>0.136</v>
       </c>
       <c r="K103" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>279</v>
@@ -5472,7 +5448,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__cpt_ep1</t>
+          <t>qwen3-8b__awq_ep3</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5482,7 +5458,7 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>cpt_ep1</t>
+          <t>awq_ep3</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -5496,22 +5472,22 @@
         </is>
       </c>
       <c r="F104" s="3" t="n">
-        <v>0.55</v>
+        <v>0.618</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.584</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>-0.016</v>
+        <v>0.034</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>-0.054</v>
+        <v>-0.007</v>
       </c>
       <c r="J104" s="3" t="n">
-        <v>0.022</v>
+        <v>0.075</v>
       </c>
       <c r="K104" s="3" t="n">
-        <v>0.431</v>
+        <v>0.126</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>279</v>
@@ -5520,7 +5496,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__cpt_ep1</t>
+          <t>qwen3-8b__awq_ep3</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5530,7 +5506,7 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>cpt_ep1</t>
+          <t>awq_ep3</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -5543,32 +5519,20 @@
           <t>keyfact_recall</t>
         </is>
       </c>
-      <c r="F105" s="3" t="n">
-        <v>0.341</v>
-      </c>
-      <c r="G105" s="3" t="n">
-        <v>0.331</v>
-      </c>
-      <c r="H105" s="3" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I105" s="3" t="n">
-        <v>-0.025</v>
-      </c>
-      <c r="J105" s="3" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="K105" s="3" t="n">
-        <v>0.579</v>
-      </c>
+      <c r="F105" s="3" t="n"/>
+      <c r="G105" s="3" t="n"/>
+      <c r="H105" s="3" t="n"/>
+      <c r="I105" s="3" t="n"/>
+      <c r="J105" s="3" t="n"/>
+      <c r="K105" s="3" t="n"/>
       <c r="L105" s="2" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__cpt_ep1</t>
+          <t>qwen3-8b__awq_ep3</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5578,7 +5542,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>cpt_ep1</t>
+          <t>awq_ep3</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -5592,22 +5556,22 @@
         </is>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.043</v>
+        <v>0.244</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.011</v>
+        <v>0.029</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0.032</v>
+        <v>0.215</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0.014</v>
+        <v>0.165</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0.054</v>
+        <v>0.269</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>279</v>
@@ -5616,7 +5580,7 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__cpt_ep1__bf16serve</t>
+          <t>qwen3-8b__base</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5626,12 +5590,12 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>cpt_ep1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -5640,31 +5604,31 @@
         </is>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.647</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0.575</v>
+        <v>0.649</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>-0.016</v>
+        <v>-0.002</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>-0.054</v>
+        <v>-0.045</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>0.02</v>
+        <v>0.038</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>0.433</v>
+        <v>0.965</v>
       </c>
       <c r="L107" s="2" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__cpt_ep1__bf16serve</t>
+          <t>qwen3-8b__base</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -5674,12 +5638,12 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>cpt_ep1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -5688,22 +5652,22 @@
         </is>
       </c>
       <c r="F108" s="3" t="n">
-        <v>0.353</v>
+        <v>0.547</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>0.333</v>
+        <v>0.523</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>0.02</v>
+        <v>0.025</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>-0.019</v>
+        <v>-0.007</v>
       </c>
       <c r="J108" s="3" t="n">
-        <v>0.059</v>
+        <v>0.056</v>
       </c>
       <c r="K108" s="3" t="n">
-        <v>0.32</v>
+        <v>0.14</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>279</v>
@@ -5712,7 +5676,7 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__cpt_ep1__bf16serve</t>
+          <t>qwen3-8b__base</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5722,12 +5686,12 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>cpt_ep1</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -5736,22 +5700,22 @@
         </is>
       </c>
       <c r="F109" s="3" t="n">
-        <v>0.022</v>
+        <v>0</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="H109" s="3" t="n">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="I109" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J109" s="3" t="n">
-        <v>0.036</v>
+        <v>0</v>
       </c>
       <c r="K109" s="3" t="n">
-        <v>0.08699999999999999</v>
+        <v>1</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>279</v>
@@ -5760,7 +5724,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__ep1</t>
+          <t>qwen3-8b__concise40</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5770,7 +5734,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>ep1</t>
+          <t>concise40</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -5784,22 +5748,22 @@
         </is>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0.57</v>
+        <v>0.522</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0.599</v>
+        <v>0.582</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>-0.029</v>
+        <v>-0.061</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>-0.068</v>
+        <v>-0.102</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0.011</v>
+        <v>-0.023</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0.183</v>
+        <v>0.002</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>279</v>
@@ -5808,7 +5772,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__ep1</t>
+          <t>qwen3-8b__concise40</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5818,7 +5782,7 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>ep1</t>
+          <t>concise40</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -5832,22 +5796,22 @@
         </is>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0.392</v>
+        <v>0.334</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0.338</v>
+        <v>0.316</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0.054</v>
+        <v>0.018</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0.016</v>
+        <v>-0.014</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0.096</v>
+        <v>0.048</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0.008</v>
+        <v>0.281</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>279</v>
@@ -5856,7 +5820,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__ep1</t>
+          <t>qwen3-8b__concise40</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5866,7 +5830,7 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>ep1</t>
+          <t>concise40</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -5880,22 +5844,22 @@
         </is>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0.07199999999999999</v>
+        <v>0</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0.057</v>
+        <v>0</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0.029</v>
+        <v>0</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>279</v>
@@ -5904,7 +5868,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__ep1__bf16serve</t>
+          <t>qwen3-8b__cpt_ep1</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -5914,12 +5878,12 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>ep1</t>
+          <t>cpt_ep1</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -5928,22 +5892,22 @@
         </is>
       </c>
       <c r="F113" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G113" s="3" t="n">
         <v>0.5659999999999999</v>
       </c>
-      <c r="G113" s="3" t="n">
-        <v>0.573</v>
-      </c>
       <c r="H113" s="3" t="n">
-        <v>-0.007</v>
+        <v>-0.016</v>
       </c>
       <c r="I113" s="3" t="n">
-        <v>-0.045</v>
+        <v>-0.054</v>
       </c>
       <c r="J113" s="3" t="n">
-        <v>0.032</v>
+        <v>0.022</v>
       </c>
       <c r="K113" s="3" t="n">
-        <v>0.758</v>
+        <v>0.431</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>279</v>
@@ -5952,7 +5916,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__ep1__bf16serve</t>
+          <t>qwen3-8b__cpt_ep1</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -5962,12 +5926,12 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>ep1</t>
+          <t>cpt_ep1</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -5976,22 +5940,22 @@
         </is>
       </c>
       <c r="F114" s="3" t="n">
-        <v>0.379</v>
+        <v>0.341</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0.338</v>
+        <v>0.331</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>0.041</v>
+        <v>0.01</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>-0.001</v>
+        <v>-0.025</v>
       </c>
       <c r="J114" s="3" t="n">
-        <v>0.081</v>
+        <v>0.046</v>
       </c>
       <c r="K114" s="3" t="n">
-        <v>0.051</v>
+        <v>0.579</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>279</v>
@@ -6000,7 +5964,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__ep1__bf16serve</t>
+          <t>qwen3-8b__cpt_ep1</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -6010,12 +5974,12 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>ep1</t>
+          <t>cpt_ep1</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -6024,22 +5988,22 @@
         </is>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0.057</v>
+        <v>0.043</v>
       </c>
       <c r="G115" s="3" t="n">
         <v>0.011</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0.047</v>
+        <v>0.032</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0.022</v>
+        <v>0.014</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.054</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>279</v>
@@ -6048,7 +6012,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__ep2</t>
+          <t>qwen3-8b__cpt_ep1__bf16serve</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -6058,12 +6022,12 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>ep2</t>
+          <t>cpt_ep1</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>bf16serve</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -6072,31 +6036,31 @@
         </is>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0.746</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0.627</v>
+        <v>0.575</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0.118</v>
+        <v>-0.016</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0.073</v>
+        <v>-0.054</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0.158</v>
+        <v>0.02</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>0.433</v>
       </c>
       <c r="L116" s="2" t="n">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__ep2</t>
+          <t>qwen3-8b__cpt_ep1__bf16serve</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -6106,12 +6070,12 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>ep2</t>
+          <t>cpt_ep1</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>bf16serve</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -6120,22 +6084,22 @@
         </is>
       </c>
       <c r="F117" s="3" t="n">
-        <v>0.654</v>
+        <v>0.353</v>
       </c>
       <c r="G117" s="3" t="n">
-        <v>0.404</v>
+        <v>0.333</v>
       </c>
       <c r="H117" s="3" t="n">
-        <v>0.25</v>
+        <v>0.02</v>
       </c>
       <c r="I117" s="3" t="n">
-        <v>0.201</v>
+        <v>-0.019</v>
       </c>
       <c r="J117" s="3" t="n">
-        <v>0.297</v>
+        <v>0.059</v>
       </c>
       <c r="K117" s="3" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="L117" s="2" t="n">
         <v>279</v>
@@ -6144,7 +6108,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__ep2</t>
+          <t>qwen3-8b__cpt_ep1__bf16serve</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -6154,12 +6118,12 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>ep2</t>
+          <t>cpt_ep1</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>bf16serve</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -6168,22 +6132,22 @@
         </is>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0.523</v>
+        <v>0.022</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0.061</v>
+        <v>0.004</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0.462</v>
+        <v>0.018</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0.405</v>
+        <v>0</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0.523</v>
+        <v>0.036</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="L118" s="2" t="n">
         <v>279</v>
@@ -6192,7 +6156,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__ep2__bf16serve</t>
+          <t>qwen3-8b__ep1</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -6202,12 +6166,12 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>ep2</t>
+          <t>ep1</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -6216,22 +6180,22 @@
         </is>
       </c>
       <c r="F119" s="3" t="n">
-        <v>0.654</v>
+        <v>0.57</v>
       </c>
       <c r="G119" s="3" t="n">
-        <v>0.59</v>
+        <v>0.599</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>0.065</v>
+        <v>-0.029</v>
       </c>
       <c r="I119" s="3" t="n">
-        <v>0.022</v>
+        <v>-0.068</v>
       </c>
       <c r="J119" s="3" t="n">
-        <v>0.106</v>
+        <v>0.011</v>
       </c>
       <c r="K119" s="3" t="n">
-        <v>0.003</v>
+        <v>0.183</v>
       </c>
       <c r="L119" s="2" t="n">
         <v>279</v>
@@ -6240,7 +6204,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__ep2__bf16serve</t>
+          <t>qwen3-8b__ep1</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -6250,12 +6214,12 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>ep2</t>
+          <t>ep1</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -6264,22 +6228,22 @@
         </is>
       </c>
       <c r="F120" s="3" t="n">
-        <v>0.492</v>
+        <v>0.392</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>0.426</v>
+        <v>0.338</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>0.066</v>
+        <v>0.054</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>0.024</v>
+        <v>0.016</v>
       </c>
       <c r="J120" s="3" t="n">
-        <v>0.111</v>
+        <v>0.096</v>
       </c>
       <c r="K120" s="3" t="n">
-        <v>0.005</v>
+        <v>0.008</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>279</v>
@@ -6288,7 +6252,7 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__ep2__bf16serve</t>
+          <t>qwen3-8b__ep1</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -6298,12 +6262,12 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>ep2</t>
+          <t>ep1</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -6312,19 +6276,19 @@
         </is>
       </c>
       <c r="F121" s="3" t="n">
-        <v>0.194</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>0.025</v>
+        <v>0.014</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>0.168</v>
+        <v>0.057</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>0.122</v>
+        <v>0.029</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>0.215</v>
+        <v>0.09</v>
       </c>
       <c r="K121" s="3" t="n">
         <v>0</v>
@@ -6336,7 +6300,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__ep3</t>
+          <t>qwen3-8b__ep1__bf16serve</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -6346,12 +6310,12 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>ep3</t>
+          <t>ep1</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>bf16serve</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -6360,31 +6324,31 @@
         </is>
       </c>
       <c r="F122" s="3" t="n">
-        <v>0.828</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>0.619</v>
+        <v>0.573</v>
       </c>
       <c r="H122" s="3" t="n">
-        <v>0.209</v>
+        <v>-0.007</v>
       </c>
       <c r="I122" s="3" t="n">
-        <v>0.164</v>
+        <v>-0.045</v>
       </c>
       <c r="J122" s="3" t="n">
-        <v>0.255</v>
+        <v>0.032</v>
       </c>
       <c r="K122" s="3" t="n">
-        <v>0</v>
+        <v>0.758</v>
       </c>
       <c r="L122" s="2" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__ep3</t>
+          <t>qwen3-8b__ep1__bf16serve</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -6394,12 +6358,12 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>ep3</t>
+          <t>ep1</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>bf16serve</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -6408,22 +6372,22 @@
         </is>
       </c>
       <c r="F123" s="3" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.379</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>0.402</v>
+        <v>0.338</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>0.28</v>
+        <v>0.041</v>
       </c>
       <c r="I123" s="3" t="n">
-        <v>0.23</v>
+        <v>-0.001</v>
       </c>
       <c r="J123" s="3" t="n">
-        <v>0.335</v>
+        <v>0.081</v>
       </c>
       <c r="K123" s="3" t="n">
-        <v>0</v>
+        <v>0.051</v>
       </c>
       <c r="L123" s="2" t="n">
         <v>279</v>
@@ -6432,7 +6396,7 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__ep3</t>
+          <t>qwen3-8b__ep1__bf16serve</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -6442,12 +6406,12 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>ep3</t>
+          <t>ep1</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>bf16serve</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -6456,19 +6420,19 @@
         </is>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0.606</v>
+        <v>0.057</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0.05</v>
+        <v>0.011</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0.556</v>
+        <v>0.047</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0.498</v>
+        <v>0.022</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0.616</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="K124" s="3" t="n">
         <v>0</v>
@@ -6480,7 +6444,7 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__ep3__bf16serve</t>
+          <t>qwen3-8b__ep2</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -6490,12 +6454,12 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>ep3</t>
+          <t>ep2</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -6504,22 +6468,22 @@
         </is>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0.642</v>
+        <v>0.746</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0.584</v>
+        <v>0.627</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0.057</v>
+        <v>0.118</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0.014</v>
+        <v>0.073</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0.099</v>
+        <v>0.158</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="L125" s="2" t="n">
         <v>279</v>
@@ -6528,7 +6492,7 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__ep3__bf16serve</t>
+          <t>qwen3-8b__ep2</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -6538,12 +6502,12 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>ep3</t>
+          <t>ep2</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -6552,19 +6516,19 @@
         </is>
       </c>
       <c r="F126" s="3" t="n">
-        <v>0.516</v>
+        <v>0.654</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>0.407</v>
+        <v>0.404</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>0.109</v>
+        <v>0.25</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>0.063</v>
+        <v>0.201</v>
       </c>
       <c r="J126" s="3" t="n">
-        <v>0.155</v>
+        <v>0.297</v>
       </c>
       <c r="K126" s="3" t="n">
         <v>0</v>
@@ -6576,7 +6540,7 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__ep3__bf16serve</t>
+          <t>qwen3-8b__ep2</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -6586,12 +6550,12 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>ep3</t>
+          <t>ep2</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -6600,19 +6564,19 @@
         </is>
       </c>
       <c r="F127" s="3" t="n">
-        <v>0.215</v>
+        <v>0.523</v>
       </c>
       <c r="G127" s="3" t="n">
-        <v>0.025</v>
+        <v>0.061</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>0.19</v>
+        <v>0.462</v>
       </c>
       <c r="I127" s="3" t="n">
-        <v>0.143</v>
+        <v>0.405</v>
       </c>
       <c r="J127" s="3" t="n">
-        <v>0.24</v>
+        <v>0.523</v>
       </c>
       <c r="K127" s="3" t="n">
         <v>0</v>
@@ -6624,7 +6588,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__ft1run</t>
+          <t>qwen3-8b__ep2__bf16serve</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -6634,12 +6598,12 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>ft1run</t>
+          <t>ep2</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>bf16serve</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -6648,31 +6612,31 @@
         </is>
       </c>
       <c r="F128" s="3" t="n">
-        <v>0.543</v>
+        <v>0.654</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>0.543</v>
+        <v>0.59</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>0</v>
+        <v>0.065</v>
       </c>
       <c r="I128" s="3" t="n">
-        <v>-0.038</v>
+        <v>0.022</v>
       </c>
       <c r="J128" s="3" t="n">
-        <v>0.038</v>
+        <v>0.106</v>
       </c>
       <c r="K128" s="3" t="n">
-        <v>1</v>
+        <v>0.003</v>
       </c>
       <c r="L128" s="2" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__ft1run</t>
+          <t>qwen3-8b__ep2__bf16serve</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -6682,12 +6646,12 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>ft1run</t>
+          <t>ep2</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>bf16serve</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -6696,22 +6660,22 @@
         </is>
       </c>
       <c r="F129" s="3" t="n">
-        <v>0.364</v>
+        <v>0.492</v>
       </c>
       <c r="G129" s="3" t="n">
-        <v>0.346</v>
+        <v>0.426</v>
       </c>
       <c r="H129" s="3" t="n">
-        <v>0.018</v>
+        <v>0.066</v>
       </c>
       <c r="I129" s="3" t="n">
-        <v>-0.021</v>
+        <v>0.024</v>
       </c>
       <c r="J129" s="3" t="n">
-        <v>0.055</v>
+        <v>0.111</v>
       </c>
       <c r="K129" s="3" t="n">
-        <v>0.359</v>
+        <v>0.005</v>
       </c>
       <c r="L129" s="2" t="n">
         <v>279</v>
@@ -6720,7 +6684,7 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__ft1run</t>
+          <t>qwen3-8b__ep2__bf16serve</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -6730,12 +6694,12 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>ft1run</t>
+          <t>ep2</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>bf16serve</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -6744,22 +6708,22 @@
         </is>
       </c>
       <c r="F130" s="3" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="G130" s="3" t="n">
         <v>0.025</v>
       </c>
-      <c r="G130" s="3" t="n">
-        <v>0.007</v>
-      </c>
       <c r="H130" s="3" t="n">
-        <v>0.018</v>
+        <v>0.168</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>0</v>
+        <v>0.122</v>
       </c>
       <c r="J130" s="3" t="n">
-        <v>0.036</v>
+        <v>0.215</v>
       </c>
       <c r="K130" s="3" t="n">
-        <v>0.092</v>
+        <v>0</v>
       </c>
       <c r="L130" s="2" t="n">
         <v>279</v>
@@ -6768,7 +6732,7 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__ft1run__bf16serve</t>
+          <t>qwen3-8b__ep3</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -6778,12 +6742,12 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>ft1run</t>
+          <t>ep3</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -6792,31 +6756,31 @@
         </is>
       </c>
       <c r="F131" s="3" t="n">
-        <v>0.534</v>
+        <v>0.828</v>
       </c>
       <c r="G131" s="3" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.619</v>
       </c>
       <c r="H131" s="3" t="n">
-        <v>-0.027</v>
+        <v>0.209</v>
       </c>
       <c r="I131" s="3" t="n">
-        <v>-0.066</v>
+        <v>0.164</v>
       </c>
       <c r="J131" s="3" t="n">
-        <v>0.011</v>
+        <v>0.255</v>
       </c>
       <c r="K131" s="3" t="n">
-        <v>0.189</v>
+        <v>0</v>
       </c>
       <c r="L131" s="2" t="n">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__ft1run__bf16serve</t>
+          <t>qwen3-8b__ep3</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -6826,12 +6790,12 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>ft1run</t>
+          <t>ep3</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -6840,22 +6804,22 @@
         </is>
       </c>
       <c r="F132" s="3" t="n">
-        <v>0.35</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>0.352</v>
+        <v>0.402</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>-0.002</v>
+        <v>0.28</v>
       </c>
       <c r="I132" s="3" t="n">
-        <v>-0.041</v>
+        <v>0.23</v>
       </c>
       <c r="J132" s="3" t="n">
-        <v>0.036</v>
+        <v>0.335</v>
       </c>
       <c r="K132" s="3" t="n">
-        <v>0.905</v>
+        <v>0</v>
       </c>
       <c r="L132" s="2" t="n">
         <v>279</v>
@@ -6864,7 +6828,7 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__ft1run__bf16serve</t>
+          <t>qwen3-8b__ep3</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -6874,12 +6838,12 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>ft1run</t>
+          <t>ep3</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>bf16serve</t>
+          <t>match</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -6888,22 +6852,22 @@
         </is>
       </c>
       <c r="F133" s="3" t="n">
-        <v>0.018</v>
+        <v>0.606</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>0.011</v>
+        <v>0.05</v>
       </c>
       <c r="H133" s="3" t="n">
-        <v>0.007</v>
+        <v>0.556</v>
       </c>
       <c r="I133" s="3" t="n">
-        <v>-0.011</v>
+        <v>0.498</v>
       </c>
       <c r="J133" s="3" t="n">
-        <v>0.025</v>
+        <v>0.616</v>
       </c>
       <c r="K133" s="3" t="n">
-        <v>0.522</v>
+        <v>0</v>
       </c>
       <c r="L133" s="2" t="n">
         <v>279</v>
@@ -6912,7 +6876,7 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__nf4base</t>
+          <t>qwen3-8b__ep3__bf16serve</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -6922,12 +6886,12 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>nf4base</t>
+          <t>ep3</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>bf16serve</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -6936,31 +6900,31 @@
         </is>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0.633</v>
+        <v>0.642</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0.658</v>
+        <v>0.584</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>-0.027</v>
+        <v>0.057</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>-0.065</v>
+        <v>0.014</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0.011</v>
+        <v>0.099</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0.167</v>
+        <v>0.012</v>
       </c>
       <c r="L134" s="2" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__nf4base</t>
+          <t>qwen3-8b__ep3__bf16serve</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -6970,12 +6934,12 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>nf4base</t>
+          <t>ep3</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>bf16serve</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -6984,22 +6948,22 @@
         </is>
       </c>
       <c r="F135" s="3" t="n">
-        <v>0.531</v>
+        <v>0.516</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>0.512</v>
+        <v>0.407</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>0.019</v>
+        <v>0.109</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-0.019</v>
+        <v>0.063</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>0.055</v>
+        <v>0.155</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>0.321</v>
+        <v>0</v>
       </c>
       <c r="L135" s="2" t="n">
         <v>279</v>
@@ -7008,7 +6972,7 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__nf4base</t>
+          <t>qwen3-8b__ep3__bf16serve</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -7018,12 +6982,12 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>nf4base</t>
+          <t>ep3</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>match</t>
+          <t>bf16serve</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -7032,22 +6996,22 @@
         </is>
       </c>
       <c r="F136" s="3" t="n">
-        <v>0</v>
+        <v>0.215</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="I136" s="3" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="J136" s="3" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="K136" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L136" s="2" t="n">
         <v>279</v>
@@ -7056,7 +7020,7 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__seed43_ep1</t>
+          <t>qwen3-8b__ft1run</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -7066,7 +7030,7 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>seed43_ep1</t>
+          <t>ft1run</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
@@ -7080,31 +7044,31 @@
         </is>
       </c>
       <c r="F137" s="3" t="n">
-        <v>0.588</v>
+        <v>0.543</v>
       </c>
       <c r="G137" s="3" t="n">
-        <v>0.597</v>
+        <v>0.543</v>
       </c>
       <c r="H137" s="3" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0</v>
       </c>
       <c r="I137" s="3" t="n">
-        <v>-0.048</v>
+        <v>-0.038</v>
       </c>
       <c r="J137" s="3" t="n">
-        <v>0.03</v>
+        <v>0.038</v>
       </c>
       <c r="K137" s="3" t="n">
-        <v>0.675</v>
+        <v>1</v>
       </c>
       <c r="L137" s="2" t="n">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>qwen3-8b__seed43_ep1</t>
+          <t>qwen3-8b__ft1run</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -7114,7 +7078,7 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>seed43_ep1</t>
+          <t>ft1run</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -7128,22 +7092,22 @@
         </is>
       </c>
       <c r="F138" s="3" t="n">
-        <v>0.381</v>
+        <v>0.364</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>0.36</v>
+        <v>0.346</v>
       </c>
       <c r="H138" s="3" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
       <c r="I138" s="3" t="n">
         <v>-0.021</v>
       </c>
       <c r="J138" s="3" t="n">
-        <v>0.061</v>
+        <v>0.055</v>
       </c>
       <c r="K138" s="3" t="n">
-        <v>0.337</v>
+        <v>0.359</v>
       </c>
       <c r="L138" s="2" t="n">
         <v>279</v>
@@ -7152,48 +7116,480 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>qwen3-8b__ft1run</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>ft1run</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>exact_repro</t>
+        </is>
+      </c>
+      <c r="F139" s="3" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G139" s="3" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="H139" s="3" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="I139" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" s="3" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="K139" s="3" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="L139" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__ft1run__bf16serve</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>ft1run</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>bf16serve</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>judge_lenient</t>
+        </is>
+      </c>
+      <c r="F140" s="3" t="n">
+        <v>0.534</v>
+      </c>
+      <c r="G140" s="3" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="H140" s="3" t="n">
+        <v>-0.027</v>
+      </c>
+      <c r="I140" s="3" t="n">
+        <v>-0.066</v>
+      </c>
+      <c r="J140" s="3" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="K140" s="3" t="n">
+        <v>0.189</v>
+      </c>
+      <c r="L140" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__ft1run__bf16serve</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>ft1run</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>bf16serve</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>keyfact_recall</t>
+        </is>
+      </c>
+      <c r="F141" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G141" s="3" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="H141" s="3" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="I141" s="3" t="n">
+        <v>-0.041</v>
+      </c>
+      <c r="J141" s="3" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="K141" s="3" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="L141" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__ft1run__bf16serve</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>ft1run</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>bf16serve</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>exact_repro</t>
+        </is>
+      </c>
+      <c r="F142" s="3" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="G142" s="3" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="H142" s="3" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="I142" s="3" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="J142" s="3" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="K142" s="3" t="n">
+        <v>0.522</v>
+      </c>
+      <c r="L142" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__nf4base</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>nf4base</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>judge_lenient</t>
+        </is>
+      </c>
+      <c r="F143" s="3" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="G143" s="3" t="n">
+        <v>0.658</v>
+      </c>
+      <c r="H143" s="3" t="n">
+        <v>-0.027</v>
+      </c>
+      <c r="I143" s="3" t="n">
+        <v>-0.065</v>
+      </c>
+      <c r="J143" s="3" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="K143" s="3" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="L143" s="2" t="n">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__nf4base</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>nf4base</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>keyfact_recall</t>
+        </is>
+      </c>
+      <c r="F144" s="3" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="G144" s="3" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="H144" s="3" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="I144" s="3" t="n">
+        <v>-0.019</v>
+      </c>
+      <c r="J144" s="3" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="K144" s="3" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="L144" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__nf4base</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>nf4base</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>exact_repro</t>
+        </is>
+      </c>
+      <c r="F145" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G145" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L145" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
           <t>qwen3-8b__seed43_ep1</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>qwen3-8b</t>
         </is>
       </c>
-      <c r="C139" s="2" t="inlineStr">
+      <c r="C146" s="2" t="inlineStr">
         <is>
           <t>seed43_ep1</t>
         </is>
       </c>
-      <c r="D139" s="2" t="inlineStr">
-        <is>
-          <t>match</t>
-        </is>
-      </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>judge_lenient</t>
+        </is>
+      </c>
+      <c r="F146" s="3" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="G146" s="3" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="H146" s="3" t="n">
+        <v>-0.008999999999999999</v>
+      </c>
+      <c r="I146" s="3" t="n">
+        <v>-0.048</v>
+      </c>
+      <c r="J146" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K146" s="3" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="L146" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__seed43_ep1</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>seed43_ep1</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>keyfact_recall</t>
+        </is>
+      </c>
+      <c r="F147" s="3" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="G147" s="3" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H147" s="3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I147" s="3" t="n">
+        <v>-0.021</v>
+      </c>
+      <c r="J147" s="3" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="K147" s="3" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="L147" s="2" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b__seed43_ep1</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>qwen3-8b</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>seed43_ep1</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>match</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>exact_repro</t>
         </is>
       </c>
-      <c r="F139" s="3" t="n">
+      <c r="F148" s="3" t="n">
         <v>0.061</v>
       </c>
-      <c r="G139" s="3" t="n">
+      <c r="G148" s="3" t="n">
         <v>0.025</v>
       </c>
-      <c r="H139" s="3" t="n">
+      <c r="H148" s="3" t="n">
         <v>0.036</v>
       </c>
-      <c r="I139" s="3" t="n">
+      <c r="I148" s="3" t="n">
         <v>0.014</v>
       </c>
-      <c r="J139" s="3" t="n">
+      <c r="J148" s="3" t="n">
         <v>0.061</v>
       </c>
-      <c r="K139" s="3" t="n">
+      <c r="K148" s="3" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="L139" s="2" t="n">
+      <c r="L148" s="2" t="n">
         <v>279</v>
       </c>
     </row>

--- a/research_materials/03_results/robustness_gap.xlsx
+++ b/research_materials/03_results/robustness_gap.xlsx
@@ -459,7 +459,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Built: 2026-10-07 02:47 by src/build_research_materials.py</t>
+          <t>Built: 2026-10-07 02:57 by src/build_research_materials.py</t>
         </is>
       </c>
     </row>
@@ -647,14 +647,26 @@
           <t>keyfact_recall</t>
         </is>
       </c>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="3" t="n"/>
+      <c r="F3" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0.002</v>
+      </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
     </row>
     <row r="4">
@@ -3083,14 +3095,26 @@
           <t>keyfact_recall</t>
         </is>
       </c>
-      <c r="F54" s="3" t="n"/>
-      <c r="G54" s="3" t="n"/>
-      <c r="H54" s="3" t="n"/>
-      <c r="I54" s="3" t="n"/>
-      <c r="J54" s="3" t="n"/>
-      <c r="K54" s="3" t="n"/>
+      <c r="F54" s="3" t="n">
+        <v>0.698</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>0.449</v>
+      </c>
+      <c r="H54" s="3" t="n">
+        <v>0.249</v>
+      </c>
+      <c r="I54" s="3" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="J54" s="3" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="K54" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="L54" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
     </row>
     <row r="55">
@@ -5519,14 +5543,26 @@
           <t>keyfact_recall</t>
         </is>
       </c>
-      <c r="F105" s="3" t="n"/>
-      <c r="G105" s="3" t="n"/>
-      <c r="H105" s="3" t="n"/>
-      <c r="I105" s="3" t="n"/>
-      <c r="J105" s="3" t="n"/>
-      <c r="K105" s="3" t="n"/>
+      <c r="F105" s="3" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="G105" s="3" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="H105" s="3" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="I105" s="3" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="J105" s="3" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="K105" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="L105" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
     </row>
     <row r="106">
